--- a/notebooks/data/backtest/monthly_attribution_v11.xlsx
+++ b/notebooks/data/backtest/monthly_attribution_v11.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W17"/>
+  <dimension ref="A1:W41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -554,53 +554,53 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2023-01</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.0433</v>
+        <v>0.0432</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0433</v>
+        <v>0.0432</v>
       </c>
       <c r="E2" t="n">
-        <v>3.811345761078789</v>
+        <v>4.452359636356058</v>
       </c>
       <c r="F2" t="n">
-        <v>-258196.03</v>
+        <v>6880623.67</v>
       </c>
       <c r="G2" t="n">
-        <v>521939.44</v>
+        <v>-5402948.1</v>
       </c>
       <c r="H2" t="n">
-        <v>263743.41</v>
+        <v>1477675.56</v>
       </c>
       <c r="I2" t="n">
-        <v>14310.84</v>
+        <v>14278.08</v>
       </c>
       <c r="J2" t="n">
-        <v>34378.21585577441</v>
+        <v>13072.37622940039</v>
       </c>
       <c r="K2" t="n">
-        <v>34378.22</v>
+        <v>13072.38</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>42466.6</v>
+        <v>57068.62</v>
       </c>
       <c r="N2" t="n">
-        <v>42466.6</v>
+        <v>57068.62</v>
       </c>
       <c r="O2" t="n">
-        <v>91155.66</v>
+        <v>84419.08</v>
       </c>
       <c r="P2" t="n">
-        <v>195996.4</v>
+        <v>1682538.32</v>
       </c>
       <c r="Q2" t="n">
-        <v>172587.75</v>
+        <v>1393256.48</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -612,13 +612,13 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>172587.75</v>
+        <v>1393256.48</v>
       </c>
       <c r="V2" t="n">
-        <v>172587.75</v>
+        <v>1393256.48</v>
       </c>
       <c r="W2" t="n">
-        <v>172587.75</v>
+        <v>1393256.48</v>
       </c>
     </row>
     <row r="3">
@@ -629,53 +629,53 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2023-02</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.0433</v>
+        <v>0.04556842105263158</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0433</v>
+        <v>0.0457</v>
       </c>
       <c r="E3" t="n">
-        <v>3.81280138625427</v>
+        <v>4.357481797479828</v>
       </c>
       <c r="F3" t="n">
-        <v>-3408487.6</v>
+        <v>1203575.95</v>
       </c>
       <c r="G3" t="n">
-        <v>3437810.86</v>
+        <v>-571778.3199999999</v>
       </c>
       <c r="H3" t="n">
-        <v>29323.26</v>
+        <v>631797.63</v>
       </c>
       <c r="I3" t="n">
-        <v>15933.66</v>
+        <v>3119.02</v>
       </c>
       <c r="J3" t="n">
-        <v>33587.67119537624</v>
+        <v>13504.76931277485</v>
       </c>
       <c r="K3" t="n">
-        <v>33587.67</v>
+        <v>13504.77</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>41558.08</v>
+        <v>64037.46</v>
       </c>
       <c r="N3" t="n">
-        <v>41558.08</v>
+        <v>64037.46</v>
       </c>
       <c r="O3" t="n">
-        <v>91079.41</v>
+        <v>80661.25</v>
       </c>
       <c r="P3" t="n">
-        <v>-61933.2</v>
+        <v>551136.38</v>
       </c>
       <c r="Q3" t="n">
-        <v>-61756.15</v>
+        <v>551136.38</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -687,13 +687,13 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>-61756.15</v>
+        <v>551136.38</v>
       </c>
       <c r="V3" t="n">
-        <v>-61756.15</v>
+        <v>551136.38</v>
       </c>
       <c r="W3" t="n">
-        <v>-61756.15</v>
+        <v>551136.38</v>
       </c>
     </row>
     <row r="4">
@@ -704,71 +704,71 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2023-03</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.0433</v>
+        <v>0.04644782608695652</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0433</v>
+        <v>0.0482</v>
       </c>
       <c r="E4" t="n">
-        <v>3.823328753423549</v>
+        <v>4.404158151326709</v>
       </c>
       <c r="F4" t="n">
-        <v>-1987267.31</v>
+        <v>4567079.7</v>
       </c>
       <c r="G4" t="n">
-        <v>2884272.92</v>
+        <v>-3619362.28</v>
       </c>
       <c r="H4" t="n">
-        <v>897005.61</v>
+        <v>947717.4300000001</v>
       </c>
       <c r="I4" t="n">
-        <v>13350.13</v>
+        <v>16089.23</v>
       </c>
       <c r="J4" t="n">
-        <v>39006.3186223292</v>
+        <v>16860.3842694944</v>
       </c>
       <c r="K4" t="n">
-        <v>39006.32</v>
+        <v>16860.38</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>48711.96</v>
+        <v>82226.14999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>48711.96</v>
+        <v>82226.14999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>101068.41</v>
+        <v>115175.76</v>
       </c>
       <c r="P4" t="n">
-        <v>797045.11</v>
+        <v>832541.66</v>
       </c>
       <c r="Q4" t="n">
-        <v>795937.1899999999</v>
+        <v>832541.66</v>
       </c>
       <c r="R4" t="n">
-        <v>49793.5</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>157378.03</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>207171.53</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>588765.66</v>
+        <v>832541.66</v>
       </c>
       <c r="V4" t="n">
-        <v>795937.1899999999</v>
+        <v>832541.66</v>
       </c>
       <c r="W4" t="n">
-        <v>588765.66</v>
+        <v>832541.66</v>
       </c>
     </row>
     <row r="5">
@@ -779,53 +779,53 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2023-04</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.0433</v>
+        <v>0.04818421052631579</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0433</v>
+        <v>0.0481</v>
       </c>
       <c r="E5" t="n">
-        <v>3.942722890285327</v>
+        <v>4.422568193130631</v>
       </c>
       <c r="F5" t="n">
-        <v>2351075.05</v>
+        <v>-773185</v>
       </c>
       <c r="G5" t="n">
-        <v>-1631372.8</v>
+        <v>854624.88</v>
       </c>
       <c r="H5" t="n">
-        <v>719702.25</v>
+        <v>81439.88</v>
       </c>
       <c r="I5" t="n">
-        <v>23891.13</v>
+        <v>1975.88</v>
       </c>
       <c r="J5" t="n">
-        <v>43583.60858425341</v>
+        <v>13633.11296581705</v>
       </c>
       <c r="K5" t="n">
-        <v>43583.61</v>
+        <v>13633.11</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>56150.2</v>
+        <v>73461.58</v>
       </c>
       <c r="N5" t="n">
-        <v>56150.2</v>
+        <v>73461.58</v>
       </c>
       <c r="O5" t="n">
-        <v>123624.94</v>
+        <v>89070.58</v>
       </c>
       <c r="P5" t="n">
-        <v>595751.3</v>
+        <v>-7630.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>596077.3100000001</v>
+        <v>-7630.7</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -837,13 +837,13 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>596077.3100000001</v>
+        <v>-7630.7</v>
       </c>
       <c r="V5" t="n">
-        <v>596077.3100000001</v>
+        <v>-7630.7</v>
       </c>
       <c r="W5" t="n">
-        <v>596077.3100000001</v>
+        <v>-7630.7</v>
       </c>
     </row>
     <row r="6">
@@ -854,53 +854,53 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2023-05</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.0433</v>
+        <v>0.05033181818181818</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0433</v>
+        <v>0.0507</v>
       </c>
       <c r="E6" t="n">
-        <v>4.12935680315432</v>
+        <v>4.425985619663155</v>
       </c>
       <c r="F6" t="n">
-        <v>5120213.81</v>
+        <v>4600469.93</v>
       </c>
       <c r="G6" t="n">
-        <v>-4964509.25</v>
+        <v>-3313988.43</v>
       </c>
       <c r="H6" t="n">
-        <v>155704.56</v>
+        <v>1286481.51</v>
       </c>
       <c r="I6" t="n">
-        <v>21895.88</v>
+        <v>2273.18</v>
       </c>
       <c r="J6" t="n">
-        <v>50022.51395316908</v>
+        <v>15396.91917258289</v>
       </c>
       <c r="K6" t="n">
-        <v>50022.51</v>
+        <v>15396.92</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>59239.17</v>
+        <v>92025.41</v>
       </c>
       <c r="N6" t="n">
-        <v>59239.17</v>
+        <v>92025.41</v>
       </c>
       <c r="O6" t="n">
-        <v>131157.56</v>
+        <v>109695.51</v>
       </c>
       <c r="P6" t="n">
-        <v>24367.9</v>
+        <v>1176785.99</v>
       </c>
       <c r="Q6" t="n">
-        <v>24547</v>
+        <v>1176785.99</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -912,13 +912,13 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>24547</v>
+        <v>1176785.99</v>
       </c>
       <c r="V6" t="n">
-        <v>24547</v>
+        <v>1176785.99</v>
       </c>
       <c r="W6" t="n">
-        <v>24547</v>
+        <v>1176785.99</v>
       </c>
     </row>
     <row r="7">
@@ -929,71 +929,71 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2023-06</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.0433</v>
+        <v>0.05062857142857143</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0433</v>
+        <v>0.0507</v>
       </c>
       <c r="E7" t="n">
-        <v>4.200002299812475</v>
+        <v>4.477355433767767</v>
       </c>
       <c r="F7" t="n">
-        <v>2580528.28</v>
+        <v>4248125.62</v>
       </c>
       <c r="G7" t="n">
-        <v>-2330351.52</v>
+        <v>-3138714.3</v>
       </c>
       <c r="H7" t="n">
-        <v>250176.76</v>
+        <v>1109411.32</v>
       </c>
       <c r="I7" t="n">
-        <v>13263.93</v>
+        <v>17421.65</v>
       </c>
       <c r="J7" t="n">
-        <v>50416.01612372746</v>
+        <v>17050.95163571043</v>
       </c>
       <c r="K7" t="n">
-        <v>50416.02</v>
+        <v>17050.95</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>56753.66</v>
+        <v>97857.36</v>
       </c>
       <c r="N7" t="n">
-        <v>56753.66</v>
+        <v>97857.36</v>
       </c>
       <c r="O7" t="n">
-        <v>120433.6</v>
+        <v>132329.96</v>
       </c>
       <c r="P7" t="n">
-        <v>128586.16</v>
+        <v>977081.36</v>
       </c>
       <c r="Q7" t="n">
-        <v>129743.15</v>
+        <v>977081.36</v>
       </c>
       <c r="R7" t="n">
-        <v>53985.84</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>99034.81</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>153020.65</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-23277.49</v>
+        <v>977081.36</v>
       </c>
       <c r="V7" t="n">
-        <v>129743.15</v>
+        <v>977081.36</v>
       </c>
       <c r="W7" t="n">
-        <v>-23277.49</v>
+        <v>977081.36</v>
       </c>
     </row>
     <row r="8">
@@ -1004,53 +1004,53 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2023-07</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.0433</v>
+        <v>0.05106500000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0433</v>
+        <v>0.0532</v>
       </c>
       <c r="E8" t="n">
-        <v>4.209625207174762</v>
+        <v>4.415977380432691</v>
       </c>
       <c r="F8" t="n">
-        <v>2658752.55</v>
+        <v>5943727.12</v>
       </c>
       <c r="G8" t="n">
-        <v>-2397258.53</v>
+        <v>-4604868.57</v>
       </c>
       <c r="H8" t="n">
-        <v>261494.01</v>
+        <v>1338858.56</v>
       </c>
       <c r="I8" t="n">
-        <v>17474.02</v>
+        <v>13549.03</v>
       </c>
       <c r="J8" t="n">
-        <v>65635.42833734889</v>
+        <v>20593.98963372424</v>
       </c>
       <c r="K8" t="n">
-        <v>65635.42999999999</v>
+        <v>20593.99</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>63974.81</v>
+        <v>100386.15</v>
       </c>
       <c r="N8" t="n">
-        <v>63974.81</v>
+        <v>100386.15</v>
       </c>
       <c r="O8" t="n">
-        <v>147084.26</v>
+        <v>134529.16</v>
       </c>
       <c r="P8" t="n">
-        <v>114825.17</v>
+        <v>1204329.39</v>
       </c>
       <c r="Q8" t="n">
-        <v>114409.75</v>
+        <v>1204329.39</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1062,13 +1062,13 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>114409.75</v>
+        <v>1204329.39</v>
       </c>
       <c r="V8" t="n">
-        <v>114409.75</v>
+        <v>1204329.39</v>
       </c>
       <c r="W8" t="n">
-        <v>114409.75</v>
+        <v>1204329.39</v>
       </c>
     </row>
     <row r="9">
@@ -1079,53 +1079,53 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2023-08</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.0433</v>
+        <v>0.05316521739130435</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0433</v>
+        <v>0.0532</v>
       </c>
       <c r="E9" t="n">
-        <v>4.304245489381269</v>
+        <v>4.350741971369291</v>
       </c>
       <c r="F9" t="n">
-        <v>137642.78</v>
+        <v>-1819851.32</v>
       </c>
       <c r="G9" t="n">
-        <v>175227.89</v>
+        <v>1740278.76</v>
       </c>
       <c r="H9" t="n">
-        <v>312870.67</v>
+        <v>-79572.55</v>
       </c>
       <c r="I9" t="n">
-        <v>23219.65</v>
+        <v>8832.629999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>91899.45618600416</v>
+        <v>20740.57604159077</v>
       </c>
       <c r="K9" t="n">
-        <v>91899.46000000001</v>
+        <v>20740.58</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>59348.85</v>
+        <v>115999.42</v>
       </c>
       <c r="N9" t="n">
-        <v>59348.85</v>
+        <v>115999.42</v>
       </c>
       <c r="O9" t="n">
-        <v>174467.95</v>
+        <v>145572.62</v>
       </c>
       <c r="P9" t="n">
-        <v>136315.53</v>
+        <v>-225145.18</v>
       </c>
       <c r="Q9" t="n">
-        <v>138402.71</v>
+        <v>-225145.18</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1137,13 +1137,13 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>138402.71</v>
+        <v>-225145.18</v>
       </c>
       <c r="V9" t="n">
-        <v>138402.71</v>
+        <v>-225145.18</v>
       </c>
       <c r="W9" t="n">
-        <v>138402.71</v>
+        <v>-225145.18</v>
       </c>
     </row>
     <row r="10">
@@ -1154,71 +1154,71 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2023-09</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.04226190476190476</v>
+        <v>0.05319</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0409</v>
+        <v>0.0532</v>
       </c>
       <c r="E10" t="n">
-        <v>4.378399790737683</v>
+        <v>4.55107349549287</v>
       </c>
       <c r="F10" t="n">
-        <v>3844727.98</v>
+        <v>-2903106.9</v>
       </c>
       <c r="G10" t="n">
-        <v>-3681331.67</v>
+        <v>2588131.83</v>
       </c>
       <c r="H10" t="n">
-        <v>163396.31</v>
+        <v>-314975.07</v>
       </c>
       <c r="I10" t="n">
-        <v>25522.34</v>
+        <v>13280.8</v>
       </c>
       <c r="J10" t="n">
-        <v>112104.9008354102</v>
+        <v>19027.72801088558</v>
       </c>
       <c r="K10" t="n">
-        <v>112104.9</v>
+        <v>19027.73</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>58817.33</v>
+        <v>108756.68</v>
       </c>
       <c r="N10" t="n">
-        <v>58817.33</v>
+        <v>108756.68</v>
       </c>
       <c r="O10" t="n">
-        <v>196444.58</v>
+        <v>141065.21</v>
       </c>
       <c r="P10" t="n">
-        <v>-24865.35</v>
+        <v>-452915.49</v>
       </c>
       <c r="Q10" t="n">
-        <v>-33048.26</v>
+        <v>-456040.29</v>
       </c>
       <c r="R10" t="n">
-        <v>56623.99</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>9693.540000000001</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>66317.53</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>-99365.78999999999</v>
+        <v>-456040.29</v>
       </c>
       <c r="V10" t="n">
-        <v>-33048.26</v>
+        <v>-456040.29</v>
       </c>
       <c r="W10" t="n">
-        <v>-99365.78999999999</v>
+        <v>-456040.29</v>
       </c>
     </row>
     <row r="11">
@@ -1229,53 +1229,53 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2023-10</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.04082608695652173</v>
+        <v>0.0532</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0386</v>
+        <v>0.0532</v>
       </c>
       <c r="E11" t="n">
-        <v>4.380612492229268</v>
+        <v>4.477296743353953</v>
       </c>
       <c r="F11" t="n">
-        <v>2137671.85</v>
+        <v>-1263863.76</v>
       </c>
       <c r="G11" t="n">
-        <v>-1366967.28</v>
+        <v>1376044.91</v>
       </c>
       <c r="H11" t="n">
-        <v>770704.5699999999</v>
+        <v>112181.15</v>
       </c>
       <c r="I11" t="n">
-        <v>22888.45</v>
+        <v>6226.81</v>
       </c>
       <c r="J11" t="n">
-        <v>126905.9465637682</v>
+        <v>19338.40513337572</v>
       </c>
       <c r="K11" t="n">
-        <v>126905.95</v>
+        <v>19338.41</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>62828.25</v>
+        <v>115017.85</v>
       </c>
       <c r="N11" t="n">
-        <v>62828.25</v>
+        <v>115017.85</v>
       </c>
       <c r="O11" t="n">
-        <v>212622.65</v>
+        <v>140583.06</v>
       </c>
       <c r="P11" t="n">
-        <v>557892.28</v>
+        <v>-27693.19</v>
       </c>
       <c r="Q11" t="n">
-        <v>558081.92</v>
+        <v>-28401.91</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1287,13 +1287,13 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>558081.92</v>
+        <v>-28401.91</v>
       </c>
       <c r="V11" t="n">
-        <v>558081.92</v>
+        <v>-28401.91</v>
       </c>
       <c r="W11" t="n">
-        <v>558081.92</v>
+        <v>-28401.91</v>
       </c>
     </row>
     <row r="12">
@@ -1304,53 +1304,53 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2023-11</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.03875263157894736</v>
+        <v>0.05320000000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0388</v>
+        <v>0.0532</v>
       </c>
       <c r="E12" t="n">
-        <v>4.297608822565868</v>
+        <v>4.536138951429408</v>
       </c>
       <c r="F12" t="n">
-        <v>-4593886.74</v>
+        <v>8029987.49</v>
       </c>
       <c r="G12" t="n">
-        <v>4685921.34</v>
+        <v>-6376589.96</v>
       </c>
       <c r="H12" t="n">
-        <v>92034.60000000001</v>
+        <v>1653397.53</v>
       </c>
       <c r="I12" t="n">
-        <v>35643.33</v>
+        <v>13064.29</v>
       </c>
       <c r="J12" t="n">
-        <v>105010.2141582088</v>
+        <v>23709.57949497312</v>
       </c>
       <c r="K12" t="n">
-        <v>105010.21</v>
+        <v>23709.58</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>49286.94</v>
+        <v>118615.24</v>
       </c>
       <c r="N12" t="n">
-        <v>49286.94</v>
+        <v>118615.24</v>
       </c>
       <c r="O12" t="n">
-        <v>189940.49</v>
+        <v>155389.11</v>
       </c>
       <c r="P12" t="n">
-        <v>-97044.17</v>
+        <v>1498008.41</v>
       </c>
       <c r="Q12" t="n">
-        <v>-97905.89</v>
+        <v>1498008.41</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1362,13 +1362,13 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>-97905.89</v>
+        <v>1498008.41</v>
       </c>
       <c r="V12" t="n">
-        <v>-97905.89</v>
+        <v>1498008.41</v>
       </c>
       <c r="W12" t="n">
-        <v>-97905.89</v>
+        <v>1498008.41</v>
       </c>
     </row>
     <row r="13">
@@ -1379,71 +1379,71 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2023-12</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.03731363636363637</v>
+        <v>0.0532</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0365</v>
+        <v>0.0532</v>
       </c>
       <c r="E13" t="n">
-        <v>4.391147467417974</v>
+        <v>4.426056251984564</v>
       </c>
       <c r="F13" t="n">
-        <v>-1618995.26</v>
+        <v>4380596.89</v>
       </c>
       <c r="G13" t="n">
-        <v>2360339.44</v>
+        <v>-3329898.75</v>
       </c>
       <c r="H13" t="n">
-        <v>741344.17</v>
+        <v>1050698.14</v>
       </c>
       <c r="I13" t="n">
-        <v>15630.2</v>
+        <v>10814.27</v>
       </c>
       <c r="J13" t="n">
-        <v>123890.7069284335</v>
+        <v>23775.2093502366</v>
       </c>
       <c r="K13" t="n">
-        <v>123890.71</v>
+        <v>23775.21</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>58435.41</v>
+        <v>115376.17</v>
       </c>
       <c r="N13" t="n">
-        <v>58435.41</v>
+        <v>115376.17</v>
       </c>
       <c r="O13" t="n">
-        <v>197956.32</v>
+        <v>149965.65</v>
       </c>
       <c r="P13" t="n">
-        <v>544371.0699999999</v>
+        <v>900732.49</v>
       </c>
       <c r="Q13" t="n">
-        <v>543387.86</v>
+        <v>900732.49</v>
       </c>
       <c r="R13" t="n">
-        <v>56882.21</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>135145.44</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>192027.65</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>351360.2</v>
+        <v>900732.49</v>
       </c>
       <c r="V13" t="n">
-        <v>543387.86</v>
+        <v>900732.49</v>
       </c>
       <c r="W13" t="n">
-        <v>351360.2</v>
+        <v>900732.49</v>
       </c>
     </row>
     <row r="14">
@@ -1454,53 +1454,53 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2024-01</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.03633</v>
+        <v>0.05315238095238096</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0363</v>
+        <v>0.0532</v>
       </c>
       <c r="E14" t="n">
-        <v>4.475487925093268</v>
+        <v>4.496731305638313</v>
       </c>
       <c r="F14" t="n">
-        <v>239626.94</v>
+        <v>-817014.13</v>
       </c>
       <c r="G14" t="n">
-        <v>459887.53</v>
+        <v>1055466.6</v>
       </c>
       <c r="H14" t="n">
-        <v>699514.47</v>
+        <v>238452.47</v>
       </c>
       <c r="I14" t="n">
-        <v>25581.06</v>
+        <v>12473.63</v>
       </c>
       <c r="J14" t="n">
-        <v>121689.5608631636</v>
+        <v>23009.65770842694</v>
       </c>
       <c r="K14" t="n">
-        <v>121689.56</v>
+        <v>23009.66</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>55488.07</v>
+        <v>125436.41</v>
       </c>
       <c r="N14" t="n">
-        <v>55488.07</v>
+        <v>125436.41</v>
       </c>
       <c r="O14" t="n">
-        <v>202758.69</v>
+        <v>160919.7</v>
       </c>
       <c r="P14" t="n">
-        <v>497210.93</v>
+        <v>74367.95</v>
       </c>
       <c r="Q14" t="n">
-        <v>496755.79</v>
+        <v>77532.77</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1512,13 +1512,13 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>496755.79</v>
+        <v>77532.77</v>
       </c>
       <c r="V14" t="n">
-        <v>496755.79</v>
+        <v>77532.77</v>
       </c>
       <c r="W14" t="n">
-        <v>496755.79</v>
+        <v>77532.77</v>
       </c>
     </row>
     <row r="15">
@@ -1529,53 +1529,53 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.03633157894736842</v>
+        <v>0.05316</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0363</v>
+        <v>0.0532</v>
       </c>
       <c r="E15" t="n">
-        <v>4.311362408803539</v>
+        <v>4.462218364970779</v>
       </c>
       <c r="F15" t="n">
-        <v>-2985846.05</v>
+        <v>10162412.47</v>
       </c>
       <c r="G15" t="n">
-        <v>4203252.44</v>
+        <v>-9482168.65</v>
       </c>
       <c r="H15" t="n">
-        <v>1217406.39</v>
+        <v>680243.8199999999</v>
       </c>
       <c r="I15" t="n">
-        <v>25703.61</v>
+        <v>29663.2</v>
       </c>
       <c r="J15" t="n">
-        <v>132530.3007955821</v>
+        <v>23040.9564214907</v>
       </c>
       <c r="K15" t="n">
-        <v>132530.3</v>
+        <v>23040.96</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>53434.08</v>
+        <v>122262.18</v>
       </c>
       <c r="N15" t="n">
-        <v>53434.08</v>
+        <v>122262.18</v>
       </c>
       <c r="O15" t="n">
-        <v>211667.99</v>
+        <v>174966.33</v>
       </c>
       <c r="P15" t="n">
-        <v>1005941.77</v>
+        <v>505277.49</v>
       </c>
       <c r="Q15" t="n">
-        <v>1005738.4</v>
+        <v>505277.49</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -1587,13 +1587,13 @@
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1005738.4</v>
+        <v>505277.49</v>
       </c>
       <c r="V15" t="n">
-        <v>1005738.4</v>
+        <v>505277.49</v>
       </c>
       <c r="W15" t="n">
-        <v>1005738.4</v>
+        <v>505277.49</v>
       </c>
     </row>
     <row r="16">
@@ -1604,71 +1604,71 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2024-03</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.03638181818181818</v>
+        <v>0.05318000000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0364</v>
+        <v>0.0533</v>
       </c>
       <c r="E16" t="n">
-        <v>4.37956100617336</v>
+        <v>4.548256662970584</v>
       </c>
       <c r="F16" t="n">
-        <v>-993417.85</v>
+        <v>4515385.21</v>
       </c>
       <c r="G16" t="n">
-        <v>1916566.41</v>
+        <v>-4055466</v>
       </c>
       <c r="H16" t="n">
-        <v>923148.5600000001</v>
+        <v>459919.22</v>
       </c>
       <c r="I16" t="n">
-        <v>23832.4</v>
+        <v>18120.47</v>
       </c>
       <c r="J16" t="n">
-        <v>173897.5901255854</v>
+        <v>24491.00553623115</v>
       </c>
       <c r="K16" t="n">
-        <v>173897.59</v>
+        <v>24491.01</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>67203.42</v>
+        <v>126348.81</v>
       </c>
       <c r="N16" t="n">
-        <v>67203.42</v>
+        <v>126348.81</v>
       </c>
       <c r="O16" t="n">
-        <v>264933.42</v>
+        <v>168960.28</v>
       </c>
       <c r="P16" t="n">
-        <v>658175.3100000001</v>
+        <v>291497.01</v>
       </c>
       <c r="Q16" t="n">
-        <v>658215.14</v>
+        <v>290958.93</v>
       </c>
       <c r="R16" t="n">
-        <v>60482.3</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>60482.3</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>597732.84</v>
+        <v>290958.93</v>
       </c>
       <c r="V16" t="n">
-        <v>658215.14</v>
+        <v>290958.93</v>
       </c>
       <c r="W16" t="n">
-        <v>597732.84</v>
+        <v>290958.93</v>
       </c>
     </row>
     <row r="17">
@@ -1679,71 +1679,1871 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.0532</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.0532</v>
+      </c>
+      <c r="E17" t="n">
+        <v>4.542796500599895</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-2961512.53</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3241452.93</v>
+      </c>
+      <c r="H17" t="n">
+        <v>279940.4</v>
+      </c>
+      <c r="I17" t="n">
+        <v>22318.44</v>
+      </c>
+      <c r="J17" t="n">
+        <v>25774.72383318911</v>
+      </c>
+      <c r="K17" t="n">
+        <v>25774.72</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>141459.22</v>
+      </c>
+      <c r="N17" t="n">
+        <v>141459.22</v>
+      </c>
+      <c r="O17" t="n">
+        <v>189552.39</v>
+      </c>
+      <c r="P17" t="n">
+        <v>90336.85000000001</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>90388.00999999999</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>90388.00999999999</v>
+      </c>
+      <c r="V17" t="n">
+        <v>90388.00999999999</v>
+      </c>
+      <c r="W17" t="n">
+        <v>90388.00999999999</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Diamond Creek Fund</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2024-05</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.0532</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.0532</v>
+      </c>
+      <c r="E18" t="n">
+        <v>4.444485970021087</v>
+      </c>
+      <c r="F18" t="n">
+        <v>5454988.61</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-4946596.47</v>
+      </c>
+      <c r="H18" t="n">
+        <v>508392.14</v>
+      </c>
+      <c r="I18" t="n">
+        <v>14332.59</v>
+      </c>
+      <c r="J18" t="n">
+        <v>24257.79367043497</v>
+      </c>
+      <c r="K18" t="n">
+        <v>24257.79</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>138645.56</v>
+      </c>
+      <c r="N18" t="n">
+        <v>138645.56</v>
+      </c>
+      <c r="O18" t="n">
+        <v>177235.94</v>
+      </c>
+      <c r="P18" t="n">
+        <v>331156.2</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>331156.2</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>331156.2</v>
+      </c>
+      <c r="V18" t="n">
+        <v>331156.2</v>
+      </c>
+      <c r="W18" t="n">
+        <v>331156.2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Diamond Creek Fund</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2024-06</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0.0532</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.0532</v>
+      </c>
+      <c r="E19" t="n">
+        <v>4.521355755412176</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2706321.62</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-2295663.86</v>
+      </c>
+      <c r="H19" t="n">
+        <v>410657.76</v>
+      </c>
+      <c r="I19" t="n">
+        <v>9437.540000000001</v>
+      </c>
+      <c r="J19" t="n">
+        <v>21776.16099907778</v>
+      </c>
+      <c r="K19" t="n">
+        <v>21776.16</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>123215.44</v>
+      </c>
+      <c r="N19" t="n">
+        <v>123215.44</v>
+      </c>
+      <c r="O19" t="n">
+        <v>154429.14</v>
+      </c>
+      <c r="P19" t="n">
+        <v>256371.01</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>256228.62</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>256228.62</v>
+      </c>
+      <c r="V19" t="n">
+        <v>256228.62</v>
+      </c>
+      <c r="W19" t="n">
+        <v>256228.62</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Diamond Creek Fund</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.0532</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.0532</v>
+      </c>
+      <c r="E20" t="n">
+        <v>4.426572891877691</v>
+      </c>
+      <c r="F20" t="n">
+        <v>767981.64</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-331963.75</v>
+      </c>
+      <c r="H20" t="n">
+        <v>436017.88</v>
+      </c>
+      <c r="I20" t="n">
+        <v>28844.15</v>
+      </c>
+      <c r="J20" t="n">
+        <v>25498.30310047942</v>
+      </c>
+      <c r="K20" t="n">
+        <v>25498.3</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>139590.3</v>
+      </c>
+      <c r="N20" t="n">
+        <v>139590.3</v>
+      </c>
+      <c r="O20" t="n">
+        <v>193932.76</v>
+      </c>
+      <c r="P20" t="n">
+        <v>242738.96</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>242085.13</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>242085.13</v>
+      </c>
+      <c r="V20" t="n">
+        <v>242085.13</v>
+      </c>
+      <c r="W20" t="n">
+        <v>242085.13</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Diamond Creek Fund</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0.05323636363636364</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.0532</v>
+      </c>
+      <c r="E21" t="n">
+        <v>4.363798757652462</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-1667540.74</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2287334.71</v>
+      </c>
+      <c r="H21" t="n">
+        <v>619793.97</v>
+      </c>
+      <c r="I21" t="n">
+        <v>32008.56</v>
+      </c>
+      <c r="J21" t="n">
+        <v>24152.96373830043</v>
+      </c>
+      <c r="K21" t="n">
+        <v>24152.96</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>140299.27</v>
+      </c>
+      <c r="N21" t="n">
+        <v>140299.27</v>
+      </c>
+      <c r="O21" t="n">
+        <v>196460.8</v>
+      </c>
+      <c r="P21" t="n">
+        <v>423333.18</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>423333.18</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>423333.18</v>
+      </c>
+      <c r="V21" t="n">
+        <v>423333.18</v>
+      </c>
+      <c r="W21" t="n">
+        <v>423333.18</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Diamond Creek Fund</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0.0513</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.0483</v>
+      </c>
+      <c r="E22" t="n">
+        <v>4.486639914588435</v>
+      </c>
+      <c r="F22" t="n">
+        <v>3972696.69</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-4207529.14</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-234832.45</v>
+      </c>
+      <c r="I22" t="n">
+        <v>47518.96</v>
+      </c>
+      <c r="J22" t="n">
+        <v>26791.58078786265</v>
+      </c>
+      <c r="K22" t="n">
+        <v>26791.58</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>127873.27</v>
+      </c>
+      <c r="N22" t="n">
+        <v>127873.27</v>
+      </c>
+      <c r="O22" t="n">
+        <v>202183.81</v>
+      </c>
+      <c r="P22" t="n">
+        <v>-436520.65</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-437016.26</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>-437016.26</v>
+      </c>
+      <c r="V22" t="n">
+        <v>-437016.26</v>
+      </c>
+      <c r="W22" t="n">
+        <v>-437016.26</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Diamond Creek Fund</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0.0483</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.0483</v>
+      </c>
+      <c r="E23" t="n">
+        <v>4.215495283604056</v>
+      </c>
+      <c r="F23" t="n">
+        <v>138813.32</v>
+      </c>
+      <c r="G23" t="n">
+        <v>412896.6</v>
+      </c>
+      <c r="H23" t="n">
+        <v>551709.92</v>
+      </c>
+      <c r="I23" t="n">
+        <v>26176.16</v>
+      </c>
+      <c r="J23" t="n">
+        <v>59775.86802034196</v>
+      </c>
+      <c r="K23" t="n">
+        <v>59775.87</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>121644.02</v>
+      </c>
+      <c r="N23" t="n">
+        <v>121644.02</v>
+      </c>
+      <c r="O23" t="n">
+        <v>207596.05</v>
+      </c>
+      <c r="P23" t="n">
+        <v>344586.8</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>344113.87</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>344113.87</v>
+      </c>
+      <c r="V23" t="n">
+        <v>344113.87</v>
+      </c>
+      <c r="W23" t="n">
+        <v>344113.87</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Diamond Creek Fund</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.046425</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.0458</v>
+      </c>
+      <c r="E24" t="n">
+        <v>4.175718448933872</v>
+      </c>
+      <c r="F24" t="n">
+        <v>5791134.34</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-5314328.12</v>
+      </c>
+      <c r="H24" t="n">
+        <v>476806.22</v>
+      </c>
+      <c r="I24" t="n">
+        <v>36183.78</v>
+      </c>
+      <c r="J24" t="n">
+        <v>56511.55639966222</v>
+      </c>
+      <c r="K24" t="n">
+        <v>56511.56</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>101132.55</v>
+      </c>
+      <c r="N24" t="n">
+        <v>101132.55</v>
+      </c>
+      <c r="O24" t="n">
+        <v>193827.89</v>
+      </c>
+      <c r="P24" t="n">
+        <v>283420.52</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>282978.33</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>282978.33</v>
+      </c>
+      <c r="V24" t="n">
+        <v>282978.33</v>
+      </c>
+      <c r="W24" t="n">
+        <v>282978.33</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Diamond Creek Fund</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.04484761904761905</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="E25" t="n">
+        <v>4.121338594128017</v>
+      </c>
+      <c r="F25" t="n">
+        <v>181577.78</v>
+      </c>
+      <c r="G25" t="n">
+        <v>940256.71</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1121834.49</v>
+      </c>
+      <c r="I25" t="n">
+        <v>24873.21</v>
+      </c>
+      <c r="J25" t="n">
+        <v>60855.95770426944</v>
+      </c>
+      <c r="K25" t="n">
+        <v>60855.96</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>103321.14</v>
+      </c>
+      <c r="N25" t="n">
+        <v>103321.14</v>
+      </c>
+      <c r="O25" t="n">
+        <v>189050.3</v>
+      </c>
+      <c r="P25" t="n">
+        <v>934655.77</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>932784.1899999999</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>932784.1899999999</v>
+      </c>
+      <c r="V25" t="n">
+        <v>932784.1899999999</v>
+      </c>
+      <c r="W25" t="n">
+        <v>932784.1899999999</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Diamond Creek Fund</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="E26" t="n">
+        <v>4.137489713183122</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1892946.56</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-906208.83</v>
+      </c>
+      <c r="H26" t="n">
+        <v>986737.73</v>
+      </c>
+      <c r="I26" t="n">
+        <v>30682.58</v>
+      </c>
+      <c r="J26" t="n">
+        <v>62964.43117681984</v>
+      </c>
+      <c r="K26" t="n">
+        <v>62964.43</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>101823.36</v>
+      </c>
+      <c r="N26" t="n">
+        <v>101823.36</v>
+      </c>
+      <c r="O26" t="n">
+        <v>195470.38</v>
+      </c>
+      <c r="P26" t="n">
+        <v>792196.49</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>791267.36</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>791267.36</v>
+      </c>
+      <c r="V26" t="n">
+        <v>791267.36</v>
+      </c>
+      <c r="W26" t="n">
+        <v>791267.36</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Diamond Creek Fund</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="E27" t="n">
+        <v>4.155341199146508</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-4232908.25</v>
+      </c>
+      <c r="G27" t="n">
+        <v>4610498.99</v>
+      </c>
+      <c r="H27" t="n">
+        <v>377590.74</v>
+      </c>
+      <c r="I27" t="n">
+        <v>30537.96</v>
+      </c>
+      <c r="J27" t="n">
+        <v>60691.19478047488</v>
+      </c>
+      <c r="K27" t="n">
+        <v>60691.19</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>97427.12</v>
+      </c>
+      <c r="N27" t="n">
+        <v>97427.12</v>
+      </c>
+      <c r="O27" t="n">
+        <v>188656.28</v>
+      </c>
+      <c r="P27" t="n">
+        <v>188928.73</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>188934.46</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>188934.46</v>
+      </c>
+      <c r="V27" t="n">
+        <v>188934.46</v>
+      </c>
+      <c r="W27" t="n">
+        <v>188934.46</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Diamond Creek Fund</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="E28" t="n">
+        <v>4.090861249015584</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-5659232.71</v>
+      </c>
+      <c r="G28" t="n">
+        <v>7496497.58</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1837264.87</v>
+      </c>
+      <c r="I28" t="n">
+        <v>30681.67</v>
+      </c>
+      <c r="J28" t="n">
+        <v>69841.78269400471</v>
+      </c>
+      <c r="K28" t="n">
+        <v>69841.78</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>110255.22</v>
+      </c>
+      <c r="N28" t="n">
+        <v>110255.22</v>
+      </c>
+      <c r="O28" t="n">
+        <v>210778.67</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1627028.66</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1626486.2</v>
+      </c>
+      <c r="R28" t="n">
+        <v>49726.48</v>
+      </c>
+      <c r="S28" t="n">
+        <v>161578.85</v>
+      </c>
+      <c r="T28" t="n">
+        <v>211305.33</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1415180.87</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1626486.2</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1415180.87</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Diamond Creek Fund</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="E29" t="n">
+        <v>4.236666937754265</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2790749.06</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-1000868.5</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1789880.57</v>
+      </c>
+      <c r="I29" t="n">
+        <v>53706.62</v>
+      </c>
+      <c r="J29" t="n">
+        <v>83676.82151790475</v>
+      </c>
+      <c r="K29" t="n">
+        <v>83676.82000000001</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>127133.9</v>
+      </c>
+      <c r="N29" t="n">
+        <v>127133.9</v>
+      </c>
+      <c r="O29" t="n">
+        <v>264517.33</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1524956.47</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1525363.23</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1525363.23</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1525363.23</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1525363.23</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Diamond Creek Fund</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="E30" t="n">
+        <v>4.363814397757752</v>
+      </c>
+      <c r="F30" t="n">
+        <v>11479082.61</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-11180837.31</v>
+      </c>
+      <c r="H30" t="n">
+        <v>298245.3</v>
+      </c>
+      <c r="I30" t="n">
+        <v>43914.33</v>
+      </c>
+      <c r="J30" t="n">
+        <v>95038.97805236513</v>
+      </c>
+      <c r="K30" t="n">
+        <v>95038.98</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>134261.49</v>
+      </c>
+      <c r="N30" t="n">
+        <v>134261.49</v>
+      </c>
+      <c r="O30" t="n">
+        <v>273214.8</v>
+      </c>
+      <c r="P30" t="n">
+        <v>24989.21</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>25030.49</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>25030.49</v>
+      </c>
+      <c r="V30" t="n">
+        <v>25030.49</v>
+      </c>
+      <c r="W30" t="n">
+        <v>25030.49</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Diamond Creek Fund</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="E31" t="n">
+        <v>4.408082645713115</v>
+      </c>
+      <c r="F31" t="n">
+        <v>7203948.29</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-6874363.66</v>
+      </c>
+      <c r="H31" t="n">
+        <v>329584.62</v>
+      </c>
+      <c r="I31" t="n">
+        <v>29620.42</v>
+      </c>
+      <c r="J31" t="n">
+        <v>95558.18968603574</v>
+      </c>
+      <c r="K31" t="n">
+        <v>95558.19</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>129553.09</v>
+      </c>
+      <c r="N31" t="n">
+        <v>129553.09</v>
+      </c>
+      <c r="O31" t="n">
+        <v>254731.7</v>
+      </c>
+      <c r="P31" t="n">
+        <v>73913.24000000001</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>74852.92</v>
+      </c>
+      <c r="R31" t="n">
+        <v>54103.88</v>
+      </c>
+      <c r="S31" t="n">
+        <v>126633.47</v>
+      </c>
+      <c r="T31" t="n">
+        <v>180737.34</v>
+      </c>
+      <c r="U31" t="n">
+        <v>-105884.42</v>
+      </c>
+      <c r="V31" t="n">
+        <v>74852.92</v>
+      </c>
+      <c r="W31" t="n">
+        <v>-105884.42</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Diamond Creek Fund</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="E32" t="n">
+        <v>4.297217936857737</v>
+      </c>
+      <c r="F32" t="n">
+        <v>5095142.2</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-4517555.05</v>
+      </c>
+      <c r="H32" t="n">
+        <v>577587.16</v>
+      </c>
+      <c r="I32" t="n">
+        <v>29371</v>
+      </c>
+      <c r="J32" t="n">
+        <v>118008.8512909473</v>
+      </c>
+      <c r="K32" t="n">
+        <v>118008.85</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>139638.35</v>
+      </c>
+      <c r="N32" t="n">
+        <v>139638.35</v>
+      </c>
+      <c r="O32" t="n">
+        <v>287018.19</v>
+      </c>
+      <c r="P32" t="n">
+        <v>290970.96</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>290568.96</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>290568.96</v>
+      </c>
+      <c r="V32" t="n">
+        <v>290568.96</v>
+      </c>
+      <c r="W32" t="n">
+        <v>290568.96</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Diamond Creek Fund</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="E33" t="n">
+        <v>4.344970811214985</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1030043.33</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-438766.11</v>
+      </c>
+      <c r="H33" t="n">
+        <v>591277.21</v>
+      </c>
+      <c r="I33" t="n">
+        <v>44919.02</v>
+      </c>
+      <c r="J33" t="n">
+        <v>139057.3941616204</v>
+      </c>
+      <c r="K33" t="n">
+        <v>139057.39</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>133537.45</v>
+      </c>
+      <c r="N33" t="n">
+        <v>133537.45</v>
+      </c>
+      <c r="O33" t="n">
+        <v>317513.87</v>
+      </c>
+      <c r="P33" t="n">
+        <v>271767.73</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>273763.35</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>273763.35</v>
+      </c>
+      <c r="V33" t="n">
+        <v>273763.35</v>
+      </c>
+      <c r="W33" t="n">
+        <v>273763.35</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Diamond Creek Fund</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.04226190476190476</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.0409</v>
+      </c>
+      <c r="E34" t="n">
+        <v>4.42954398510511</v>
+      </c>
+      <c r="F34" t="n">
+        <v>8685515.630000001</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-8464296.300000001</v>
+      </c>
+      <c r="H34" t="n">
+        <v>221219.33</v>
+      </c>
+      <c r="I34" t="n">
+        <v>43220.46</v>
+      </c>
+      <c r="J34" t="n">
+        <v>160403.0118349085</v>
+      </c>
+      <c r="K34" t="n">
+        <v>160403.01</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>135288.18</v>
+      </c>
+      <c r="N34" t="n">
+        <v>135288.18</v>
+      </c>
+      <c r="O34" t="n">
+        <v>338911.64</v>
+      </c>
+      <c r="P34" t="n">
+        <v>-111571.62</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>-117692.32</v>
+      </c>
+      <c r="R34" t="n">
+        <v>57534.55</v>
+      </c>
+      <c r="S34" t="n">
+        <v>30464.21</v>
+      </c>
+      <c r="T34" t="n">
+        <v>87998.75999999999</v>
+      </c>
+      <c r="U34" t="n">
+        <v>-205691.08</v>
+      </c>
+      <c r="V34" t="n">
+        <v>-117692.32</v>
+      </c>
+      <c r="W34" t="n">
+        <v>-205691.08</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Diamond Creek Fund</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.04082608695652173</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.0386</v>
+      </c>
+      <c r="E35" t="n">
+        <v>4.426901975209142</v>
+      </c>
+      <c r="F35" t="n">
+        <v>4695393.16</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-3679490.96</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1015902.21</v>
+      </c>
+      <c r="I35" t="n">
+        <v>45056.16</v>
+      </c>
+      <c r="J35" t="n">
+        <v>178750.1068107546</v>
+      </c>
+      <c r="K35" t="n">
+        <v>178750.11</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>142812.25</v>
+      </c>
+      <c r="N35" t="n">
+        <v>142812.25</v>
+      </c>
+      <c r="O35" t="n">
+        <v>366618.52</v>
+      </c>
+      <c r="P35" t="n">
+        <v>648975.7</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>649283.6899999999</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>649283.6899999999</v>
+      </c>
+      <c r="V35" t="n">
+        <v>649283.6899999999</v>
+      </c>
+      <c r="W35" t="n">
+        <v>649283.6899999999</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Diamond Creek Fund</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.03875263157894736</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.0388</v>
+      </c>
+      <c r="E36" t="n">
+        <v>4.344185305810045</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-6633788.74</v>
+      </c>
+      <c r="G36" t="n">
+        <v>6695326.9</v>
+      </c>
+      <c r="H36" t="n">
+        <v>61538.16</v>
+      </c>
+      <c r="I36" t="n">
+        <v>62925.21</v>
+      </c>
+      <c r="J36" t="n">
+        <v>150432.8249113848</v>
+      </c>
+      <c r="K36" t="n">
+        <v>150432.82</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>111024.93</v>
+      </c>
+      <c r="N36" t="n">
+        <v>111024.93</v>
+      </c>
+      <c r="O36" t="n">
+        <v>324382.96</v>
+      </c>
+      <c r="P36" t="n">
+        <v>-261987.01</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>-262844.8</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>-262844.8</v>
+      </c>
+      <c r="V36" t="n">
+        <v>-262844.8</v>
+      </c>
+      <c r="W36" t="n">
+        <v>-262844.8</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Diamond Creek Fund</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.03731363636363637</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.0365</v>
+      </c>
+      <c r="E37" t="n">
+        <v>4.423680303176043</v>
+      </c>
+      <c r="F37" t="n">
+        <v>-1374943.16</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2580772.76</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1205829.6</v>
+      </c>
+      <c r="I37" t="n">
+        <v>27240.89</v>
+      </c>
+      <c r="J37" t="n">
+        <v>182891.2053595921</v>
+      </c>
+      <c r="K37" t="n">
+        <v>182891.21</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>129025.77</v>
+      </c>
+      <c r="N37" t="n">
+        <v>129025.77</v>
+      </c>
+      <c r="O37" t="n">
+        <v>339157.86</v>
+      </c>
+      <c r="P37" t="n">
+        <v>867701.3100000001</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>866671.75</v>
+      </c>
+      <c r="R37" t="n">
+        <v>58359.87</v>
+      </c>
+      <c r="S37" t="n">
+        <v>170825.28</v>
+      </c>
+      <c r="T37" t="n">
+        <v>229185.15</v>
+      </c>
+      <c r="U37" t="n">
+        <v>637486.59</v>
+      </c>
+      <c r="V37" t="n">
+        <v>866671.75</v>
+      </c>
+      <c r="W37" t="n">
+        <v>637486.59</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Diamond Creek Fund</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.03633</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.0363</v>
+      </c>
+      <c r="E38" t="n">
+        <v>4.500010619906295</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1413650.56</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-485014.29</v>
+      </c>
+      <c r="H38" t="n">
+        <v>928636.27</v>
+      </c>
+      <c r="I38" t="n">
+        <v>47387.28</v>
+      </c>
+      <c r="J38" t="n">
+        <v>179259.6162691689</v>
+      </c>
+      <c r="K38" t="n">
+        <v>179259.62</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>120711.47</v>
+      </c>
+      <c r="N38" t="n">
+        <v>120711.47</v>
+      </c>
+      <c r="O38" t="n">
+        <v>347358.36</v>
+      </c>
+      <c r="P38" t="n">
+        <v>581733.13</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>581277.9</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>581277.9</v>
+      </c>
+      <c r="V38" t="n">
+        <v>581277.9</v>
+      </c>
+      <c r="W38" t="n">
+        <v>581277.9</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Diamond Creek Fund</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.03633157894736842</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.0363</v>
+      </c>
+      <c r="E39" t="n">
+        <v>4.417214289881142</v>
+      </c>
+      <c r="F39" t="n">
+        <v>-4558647.76</v>
+      </c>
+      <c r="G39" t="n">
+        <v>7255317.48</v>
+      </c>
+      <c r="H39" t="n">
+        <v>2696669.72</v>
+      </c>
+      <c r="I39" t="n">
+        <v>46361.17</v>
+      </c>
+      <c r="J39" t="n">
+        <v>190487.7829969968</v>
+      </c>
+      <c r="K39" t="n">
+        <v>190487.78</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>117685.29</v>
+      </c>
+      <c r="N39" t="n">
+        <v>117685.29</v>
+      </c>
+      <c r="O39" t="n">
+        <v>354534.24</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2343913.72</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2342135.48</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2342135.48</v>
+      </c>
+      <c r="V39" t="n">
+        <v>2342135.48</v>
+      </c>
+      <c r="W39" t="n">
+        <v>2342135.48</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Diamond Creek Fund</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.03638181818181818</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.0364</v>
+      </c>
+      <c r="E40" t="n">
+        <v>4.488444548261857</v>
+      </c>
+      <c r="F40" t="n">
+        <v>-2886638.29</v>
+      </c>
+      <c r="G40" t="n">
+        <v>4343936.12</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1457297.84</v>
+      </c>
+      <c r="I40" t="n">
+        <v>45977.58</v>
+      </c>
+      <c r="J40" t="n">
+        <v>245692.2168598445</v>
+      </c>
+      <c r="K40" t="n">
+        <v>245692.22</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>147212.74</v>
+      </c>
+      <c r="N40" t="n">
+        <v>147212.74</v>
+      </c>
+      <c r="O40" t="n">
+        <v>438882.53</v>
+      </c>
+      <c r="P40" t="n">
+        <v>1018331.98</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>1018415.3</v>
+      </c>
+      <c r="R40" t="n">
+        <v>62987.77</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>62987.77</v>
+      </c>
+      <c r="U40" t="n">
+        <v>955427.53</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1018415.3</v>
+      </c>
+      <c r="W40" t="n">
+        <v>955427.53</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Diamond Creek Fund</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C41" t="n">
         <v>0.03633</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D41" t="n">
         <v>0.0363</v>
       </c>
-      <c r="E17" t="n">
-        <v>4.522878744459146</v>
-      </c>
-      <c r="F17" t="n">
-        <v>5745432.79</v>
-      </c>
-      <c r="G17" t="n">
-        <v>-13501883.17</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-7756450.38</v>
-      </c>
-      <c r="I17" t="n">
-        <v>71870.88</v>
-      </c>
-      <c r="J17" t="n">
-        <v>86983.28661384387</v>
-      </c>
-      <c r="K17" t="n">
-        <v>86983.28999999999</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>34330.57</v>
-      </c>
-      <c r="N17" t="n">
-        <v>34330.57</v>
-      </c>
-      <c r="O17" t="n">
-        <v>193184.74</v>
-      </c>
-      <c r="P17" t="n">
-        <v>-7949635.11</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>-7949635.11</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>-7949635.11</v>
-      </c>
-      <c r="V17" t="n">
-        <v>-7949635.11</v>
-      </c>
-      <c r="W17" t="n">
-        <v>-7949635.11</v>
+      <c r="E41" t="n">
+        <v>4.651764424776601</v>
+      </c>
+      <c r="F41" t="n">
+        <v>13258894.86</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-13534181.04</v>
+      </c>
+      <c r="H41" t="n">
+        <v>-275286.18</v>
+      </c>
+      <c r="I41" t="n">
+        <v>49130.02</v>
+      </c>
+      <c r="J41" t="n">
+        <v>119177.8819166915</v>
+      </c>
+      <c r="K41" t="n">
+        <v>119177.88</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>73514.16</v>
+      </c>
+      <c r="N41" t="n">
+        <v>73514.16</v>
+      </c>
+      <c r="O41" t="n">
+        <v>241822.07</v>
+      </c>
+      <c r="P41" t="n">
+        <v>-517108.25</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>-517108.25</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>-517108.25</v>
+      </c>
+      <c r="V41" t="n">
+        <v>-517108.25</v>
+      </c>
+      <c r="W41" t="n">
+        <v>-517108.25</v>
       </c>
     </row>
   </sheetData>
@@ -1829,37 +3629,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-258880.77</v>
+        <v>28944022.05</v>
       </c>
       <c r="C2" t="n">
-        <v>390011.52</v>
+        <v>1083607.9</v>
       </c>
       <c r="D2" t="n">
-        <v>1391541.74</v>
+        <v>2744572.82</v>
       </c>
       <c r="E2" t="n">
-        <v>868027.41</v>
+        <v>4602961.04</v>
       </c>
       <c r="F2" t="n">
-        <v>2649580.67</v>
+        <v>8431141.76</v>
       </c>
       <c r="G2" t="n">
-        <v>-2876998.9</v>
+        <v>20815731.02</v>
       </c>
       <c r="H2" t="n">
-        <v>-2908461.44</v>
+        <v>20512880.3</v>
       </c>
       <c r="I2" t="n">
-        <v>277767.84</v>
+        <v>282712.55</v>
       </c>
       <c r="J2" t="n">
-        <v>401251.82</v>
+        <v>489501.81</v>
       </c>
       <c r="K2" t="n">
-        <v>679019.66</v>
+        <v>772214.36</v>
       </c>
       <c r="L2" t="n">
-        <v>-3587481.09</v>
+        <v>19740665.94</v>
       </c>
     </row>
   </sheetData>

--- a/notebooks/data/backtest/monthly_attribution_v11.xlsx
+++ b/notebooks/data/backtest/monthly_attribution_v11.xlsx
@@ -564,43 +564,43 @@
         <v>0.0432</v>
       </c>
       <c r="E2" t="n">
-        <v>4.452359636356058</v>
+        <v>4.257089152151979</v>
       </c>
       <c r="F2" t="n">
-        <v>6880623.67</v>
+        <v>6179553.59</v>
       </c>
       <c r="G2" t="n">
-        <v>-5402948.1</v>
+        <v>-4934019.63</v>
       </c>
       <c r="H2" t="n">
-        <v>1477675.56</v>
+        <v>1245533.96</v>
       </c>
       <c r="I2" t="n">
-        <v>14278.08</v>
+        <v>14520.82</v>
       </c>
       <c r="J2" t="n">
-        <v>13072.37622940039</v>
+        <v>12251.11388244837</v>
       </c>
       <c r="K2" t="n">
-        <v>13072.38</v>
+        <v>12251.11</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>57068.62</v>
+        <v>54142.82</v>
       </c>
       <c r="N2" t="n">
-        <v>57068.62</v>
+        <v>54142.82</v>
       </c>
       <c r="O2" t="n">
-        <v>84419.08</v>
+        <v>80914.75</v>
       </c>
       <c r="P2" t="n">
-        <v>1682538.32</v>
+        <v>1450218.81</v>
       </c>
       <c r="Q2" t="n">
-        <v>1393256.48</v>
+        <v>1164619.21</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -612,13 +612,13 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1393256.48</v>
+        <v>1164619.21</v>
       </c>
       <c r="V2" t="n">
-        <v>1393256.48</v>
+        <v>1164619.21</v>
       </c>
       <c r="W2" t="n">
-        <v>1393256.48</v>
+        <v>1164619.21</v>
       </c>
     </row>
     <row r="3">
@@ -639,43 +639,43 @@
         <v>0.0457</v>
       </c>
       <c r="E3" t="n">
-        <v>4.357481797479828</v>
+        <v>4.149520760987008</v>
       </c>
       <c r="F3" t="n">
-        <v>1203575.95</v>
+        <v>1150488.38</v>
       </c>
       <c r="G3" t="n">
-        <v>-571778.3199999999</v>
+        <v>-510557.69</v>
       </c>
       <c r="H3" t="n">
-        <v>631797.63</v>
+        <v>639930.6800000001</v>
       </c>
       <c r="I3" t="n">
-        <v>3119.02</v>
+        <v>3112.5</v>
       </c>
       <c r="J3" t="n">
-        <v>13504.76931277485</v>
+        <v>12568.71122234015</v>
       </c>
       <c r="K3" t="n">
-        <v>13504.77</v>
+        <v>12568.71</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>64037.46</v>
+        <v>59667.54</v>
       </c>
       <c r="N3" t="n">
-        <v>64037.46</v>
+        <v>59667.54</v>
       </c>
       <c r="O3" t="n">
-        <v>80661.25</v>
+        <v>75348.75</v>
       </c>
       <c r="P3" t="n">
-        <v>551136.38</v>
+        <v>564581.9300000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>551136.38</v>
+        <v>564581.9300000001</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -687,13 +687,13 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>551136.38</v>
+        <v>564581.9300000001</v>
       </c>
       <c r="V3" t="n">
-        <v>551136.38</v>
+        <v>564581.9300000001</v>
       </c>
       <c r="W3" t="n">
-        <v>551136.38</v>
+        <v>564581.9300000001</v>
       </c>
     </row>
     <row r="4">
@@ -714,61 +714,61 @@
         <v>0.0482</v>
       </c>
       <c r="E4" t="n">
-        <v>4.404158151326709</v>
+        <v>4.207384876860384</v>
       </c>
       <c r="F4" t="n">
-        <v>4567079.7</v>
+        <v>4323329.45</v>
       </c>
       <c r="G4" t="n">
-        <v>-3619362.28</v>
+        <v>-3493421.39</v>
       </c>
       <c r="H4" t="n">
-        <v>947717.4300000001</v>
+        <v>829908.0600000001</v>
       </c>
       <c r="I4" t="n">
-        <v>16089.23</v>
+        <v>16009.24</v>
       </c>
       <c r="J4" t="n">
-        <v>16860.3842694944</v>
+        <v>15672.09570156108</v>
       </c>
       <c r="K4" t="n">
-        <v>16860.38</v>
+        <v>15672.1</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>82226.14999999999</v>
+        <v>76895.71000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>82226.14999999999</v>
+        <v>76895.71000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>115175.76</v>
+        <v>108577.04</v>
       </c>
       <c r="P4" t="n">
-        <v>832541.66</v>
+        <v>721331.02</v>
       </c>
       <c r="Q4" t="n">
-        <v>832541.66</v>
+        <v>721331.02</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>49738.26</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>437690.12</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>487428.37</v>
       </c>
       <c r="U4" t="n">
-        <v>832541.66</v>
+        <v>233902.65</v>
       </c>
       <c r="V4" t="n">
-        <v>832541.66</v>
+        <v>721331.02</v>
       </c>
       <c r="W4" t="n">
-        <v>832541.66</v>
+        <v>233902.65</v>
       </c>
     </row>
     <row r="5">
@@ -789,43 +789,43 @@
         <v>0.0481</v>
       </c>
       <c r="E5" t="n">
-        <v>4.422568193130631</v>
+        <v>4.242716035080737</v>
       </c>
       <c r="F5" t="n">
-        <v>-773185</v>
+        <v>-737545.4</v>
       </c>
       <c r="G5" t="n">
-        <v>854624.88</v>
+        <v>816416.16</v>
       </c>
       <c r="H5" t="n">
-        <v>81439.88</v>
+        <v>78870.75999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>1975.88</v>
+        <v>1984.76</v>
       </c>
       <c r="J5" t="n">
-        <v>13633.11296581705</v>
+        <v>12538.66899760892</v>
       </c>
       <c r="K5" t="n">
-        <v>13633.11</v>
+        <v>12538.67</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>73461.58</v>
+        <v>68607.23</v>
       </c>
       <c r="N5" t="n">
-        <v>73461.58</v>
+        <v>68607.23</v>
       </c>
       <c r="O5" t="n">
-        <v>89070.58</v>
+        <v>83130.67</v>
       </c>
       <c r="P5" t="n">
-        <v>-7630.7</v>
+        <v>-4259.91</v>
       </c>
       <c r="Q5" t="n">
-        <v>-7630.7</v>
+        <v>-4259.91</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -837,13 +837,13 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-7630.7</v>
+        <v>-4259.91</v>
       </c>
       <c r="V5" t="n">
-        <v>-7630.7</v>
+        <v>-4259.91</v>
       </c>
       <c r="W5" t="n">
-        <v>-7630.7</v>
+        <v>-4259.91</v>
       </c>
     </row>
     <row r="6">
@@ -864,43 +864,43 @@
         <v>0.0507</v>
       </c>
       <c r="E6" t="n">
-        <v>4.425985619663155</v>
+        <v>4.243224349689947</v>
       </c>
       <c r="F6" t="n">
-        <v>4600469.93</v>
+        <v>3794070.54</v>
       </c>
       <c r="G6" t="n">
-        <v>-3313988.43</v>
+        <v>-2700566.54</v>
       </c>
       <c r="H6" t="n">
-        <v>1286481.51</v>
+        <v>1093504</v>
       </c>
       <c r="I6" t="n">
-        <v>2273.18</v>
+        <v>2249.35</v>
       </c>
       <c r="J6" t="n">
-        <v>15396.91917258289</v>
+        <v>14208.71652464574</v>
       </c>
       <c r="K6" t="n">
-        <v>15396.92</v>
+        <v>14208.72</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>92025.41</v>
+        <v>85427.38</v>
       </c>
       <c r="N6" t="n">
-        <v>92025.41</v>
+        <v>85427.38</v>
       </c>
       <c r="O6" t="n">
-        <v>109695.51</v>
+        <v>101885.45</v>
       </c>
       <c r="P6" t="n">
-        <v>1176785.99</v>
+        <v>991618.55</v>
       </c>
       <c r="Q6" t="n">
-        <v>1176785.99</v>
+        <v>991618.55</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -912,13 +912,13 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1176785.99</v>
+        <v>991618.55</v>
       </c>
       <c r="V6" t="n">
-        <v>1176785.99</v>
+        <v>991618.55</v>
       </c>
       <c r="W6" t="n">
-        <v>1176785.99</v>
+        <v>991618.55</v>
       </c>
     </row>
     <row r="7">
@@ -939,61 +939,61 @@
         <v>0.0507</v>
       </c>
       <c r="E7" t="n">
-        <v>4.477355433767767</v>
+        <v>4.21212733025512</v>
       </c>
       <c r="F7" t="n">
-        <v>4248125.62</v>
+        <v>3001083.27</v>
       </c>
       <c r="G7" t="n">
-        <v>-3138714.3</v>
+        <v>-2223007.27</v>
       </c>
       <c r="H7" t="n">
-        <v>1109411.32</v>
+        <v>778076.01</v>
       </c>
       <c r="I7" t="n">
-        <v>17421.65</v>
+        <v>13196.99</v>
       </c>
       <c r="J7" t="n">
-        <v>17050.95163571043</v>
+        <v>15942.70043318396</v>
       </c>
       <c r="K7" t="n">
-        <v>17050.95</v>
+        <v>15942.7</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>97857.36</v>
+        <v>87569.8</v>
       </c>
       <c r="N7" t="n">
-        <v>97857.36</v>
+        <v>87569.8</v>
       </c>
       <c r="O7" t="n">
-        <v>132329.96</v>
+        <v>116709.49</v>
       </c>
       <c r="P7" t="n">
-        <v>977081.36</v>
+        <v>661366.52</v>
       </c>
       <c r="Q7" t="n">
-        <v>977081.36</v>
+        <v>661366.52</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>62536.78</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>288506.56</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>351043.35</v>
       </c>
       <c r="U7" t="n">
-        <v>977081.36</v>
+        <v>310323.17</v>
       </c>
       <c r="V7" t="n">
-        <v>977081.36</v>
+        <v>661366.52</v>
       </c>
       <c r="W7" t="n">
-        <v>977081.36</v>
+        <v>310323.17</v>
       </c>
     </row>
     <row r="8">
@@ -1014,43 +1014,43 @@
         <v>0.0532</v>
       </c>
       <c r="E8" t="n">
-        <v>4.415977380432691</v>
+        <v>4.240974625819007</v>
       </c>
       <c r="F8" t="n">
-        <v>5943727.12</v>
+        <v>5233575.63</v>
       </c>
       <c r="G8" t="n">
-        <v>-4604868.57</v>
+        <v>-4106309.44</v>
       </c>
       <c r="H8" t="n">
-        <v>1338858.56</v>
+        <v>1127266.2</v>
       </c>
       <c r="I8" t="n">
-        <v>13549.03</v>
+        <v>11169.83</v>
       </c>
       <c r="J8" t="n">
-        <v>20593.98963372424</v>
+        <v>17785.1125683979</v>
       </c>
       <c r="K8" t="n">
-        <v>20593.99</v>
+        <v>17785.11</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>100386.15</v>
+        <v>90908.25999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>100386.15</v>
+        <v>90908.25999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>134529.16</v>
+        <v>119863.2</v>
       </c>
       <c r="P8" t="n">
-        <v>1204329.39</v>
+        <v>1007403</v>
       </c>
       <c r="Q8" t="n">
-        <v>1204329.39</v>
+        <v>1007403</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1062,13 +1062,13 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1204329.39</v>
+        <v>1007403</v>
       </c>
       <c r="V8" t="n">
-        <v>1204329.39</v>
+        <v>1007403</v>
       </c>
       <c r="W8" t="n">
-        <v>1204329.39</v>
+        <v>1007403</v>
       </c>
     </row>
     <row r="9">
@@ -1089,43 +1089,43 @@
         <v>0.0532</v>
       </c>
       <c r="E9" t="n">
-        <v>4.350741971369291</v>
+        <v>4.149709044470077</v>
       </c>
       <c r="F9" t="n">
-        <v>-1819851.32</v>
+        <v>-1994816.05</v>
       </c>
       <c r="G9" t="n">
-        <v>1740278.76</v>
+        <v>1796040.41</v>
       </c>
       <c r="H9" t="n">
-        <v>-79572.55</v>
+        <v>-198775.64</v>
       </c>
       <c r="I9" t="n">
-        <v>8832.629999999999</v>
+        <v>8485.309999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>20740.57604159077</v>
+        <v>18336.49232064345</v>
       </c>
       <c r="K9" t="n">
-        <v>20740.58</v>
+        <v>18336.49</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>115999.42</v>
+        <v>102760.41</v>
       </c>
       <c r="N9" t="n">
-        <v>115999.42</v>
+        <v>102760.41</v>
       </c>
       <c r="O9" t="n">
-        <v>145572.62</v>
+        <v>129582.22</v>
       </c>
       <c r="P9" t="n">
-        <v>-225145.18</v>
+        <v>-328357.86</v>
       </c>
       <c r="Q9" t="n">
-        <v>-225145.18</v>
+        <v>-328357.86</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1137,13 +1137,13 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>-225145.18</v>
+        <v>-328357.86</v>
       </c>
       <c r="V9" t="n">
-        <v>-225145.18</v>
+        <v>-328357.86</v>
       </c>
       <c r="W9" t="n">
-        <v>-225145.18</v>
+        <v>-328357.86</v>
       </c>
     </row>
     <row r="10">
@@ -1164,61 +1164,61 @@
         <v>0.0532</v>
       </c>
       <c r="E10" t="n">
-        <v>4.55107349549287</v>
+        <v>4.374095437666899</v>
       </c>
       <c r="F10" t="n">
-        <v>-2903106.9</v>
+        <v>-2488841.93</v>
       </c>
       <c r="G10" t="n">
-        <v>2588131.83</v>
+        <v>2276618.65</v>
       </c>
       <c r="H10" t="n">
-        <v>-314975.07</v>
+        <v>-212223.28</v>
       </c>
       <c r="I10" t="n">
-        <v>13280.8</v>
+        <v>13015.89</v>
       </c>
       <c r="J10" t="n">
-        <v>19027.72801088558</v>
+        <v>16904.64097853862</v>
       </c>
       <c r="K10" t="n">
-        <v>19027.73</v>
+        <v>16904.64</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>108756.68</v>
+        <v>97664.08</v>
       </c>
       <c r="N10" t="n">
-        <v>108756.68</v>
+        <v>97664.08</v>
       </c>
       <c r="O10" t="n">
-        <v>141065.21</v>
+        <v>127584.61</v>
       </c>
       <c r="P10" t="n">
-        <v>-452915.49</v>
+        <v>-336673.53</v>
       </c>
       <c r="Q10" t="n">
-        <v>-456040.29</v>
+        <v>-339807.89</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>70973.02</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>46609.72</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>117582.74</v>
       </c>
       <c r="U10" t="n">
-        <v>-456040.29</v>
+        <v>-457390.63</v>
       </c>
       <c r="V10" t="n">
-        <v>-456040.29</v>
+        <v>-339807.89</v>
       </c>
       <c r="W10" t="n">
-        <v>-456040.29</v>
+        <v>-457390.63</v>
       </c>
     </row>
     <row r="11">
@@ -1239,43 +1239,43 @@
         <v>0.0532</v>
       </c>
       <c r="E11" t="n">
-        <v>4.477296743353953</v>
+        <v>4.307605054817456</v>
       </c>
       <c r="F11" t="n">
-        <v>-1263863.76</v>
+        <v>-1284572.35</v>
       </c>
       <c r="G11" t="n">
-        <v>1376044.91</v>
+        <v>1319948.46</v>
       </c>
       <c r="H11" t="n">
-        <v>112181.15</v>
+        <v>35376.11</v>
       </c>
       <c r="I11" t="n">
-        <v>6226.81</v>
+        <v>6140.52</v>
       </c>
       <c r="J11" t="n">
-        <v>19338.40513337572</v>
+        <v>17672.5876409492</v>
       </c>
       <c r="K11" t="n">
-        <v>19338.41</v>
+        <v>17672.59</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>115017.85</v>
+        <v>102989.19</v>
       </c>
       <c r="N11" t="n">
-        <v>115017.85</v>
+        <v>102989.19</v>
       </c>
       <c r="O11" t="n">
-        <v>140583.06</v>
+        <v>126802.29</v>
       </c>
       <c r="P11" t="n">
-        <v>-27693.19</v>
+        <v>-90471.27</v>
       </c>
       <c r="Q11" t="n">
-        <v>-28401.91</v>
+        <v>-91426.17999999999</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1287,13 +1287,13 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>-28401.91</v>
+        <v>-91426.17999999999</v>
       </c>
       <c r="V11" t="n">
-        <v>-28401.91</v>
+        <v>-91426.17999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>-28401.91</v>
+        <v>-91426.17999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1314,43 +1314,43 @@
         <v>0.0532</v>
       </c>
       <c r="E12" t="n">
-        <v>4.536138951429408</v>
+        <v>4.240405863039348</v>
       </c>
       <c r="F12" t="n">
-        <v>8029987.49</v>
+        <v>6851108.91</v>
       </c>
       <c r="G12" t="n">
-        <v>-6376589.96</v>
+        <v>-5461859.19</v>
       </c>
       <c r="H12" t="n">
-        <v>1653397.53</v>
+        <v>1389249.72</v>
       </c>
       <c r="I12" t="n">
-        <v>13064.29</v>
+        <v>17613.08</v>
       </c>
       <c r="J12" t="n">
-        <v>23709.57949497312</v>
+        <v>23491.41682691433</v>
       </c>
       <c r="K12" t="n">
-        <v>23709.58</v>
+        <v>23491.42</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>118615.24</v>
+        <v>102049.48</v>
       </c>
       <c r="N12" t="n">
-        <v>118615.24</v>
+        <v>102049.48</v>
       </c>
       <c r="O12" t="n">
-        <v>155389.11</v>
+        <v>143153.98</v>
       </c>
       <c r="P12" t="n">
-        <v>1498008.41</v>
+        <v>1246095.74</v>
       </c>
       <c r="Q12" t="n">
-        <v>1498008.41</v>
+        <v>1246095.74</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1362,13 +1362,13 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1498008.41</v>
+        <v>1246095.74</v>
       </c>
       <c r="V12" t="n">
-        <v>1498008.41</v>
+        <v>1246095.74</v>
       </c>
       <c r="W12" t="n">
-        <v>1498008.41</v>
+        <v>1246095.74</v>
       </c>
     </row>
     <row r="13">
@@ -1389,61 +1389,61 @@
         <v>0.0532</v>
       </c>
       <c r="E13" t="n">
-        <v>4.426056251984564</v>
+        <v>4.23593447545381</v>
       </c>
       <c r="F13" t="n">
-        <v>4380596.89</v>
+        <v>4231190.08</v>
       </c>
       <c r="G13" t="n">
-        <v>-3329898.75</v>
+        <v>-3170000.87</v>
       </c>
       <c r="H13" t="n">
-        <v>1050698.14</v>
+        <v>1061189.21</v>
       </c>
       <c r="I13" t="n">
-        <v>10814.27</v>
+        <v>12778.73</v>
       </c>
       <c r="J13" t="n">
-        <v>23775.2093502366</v>
+        <v>25732.77410576204</v>
       </c>
       <c r="K13" t="n">
-        <v>23775.21</v>
+        <v>25732.77</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>115376.17</v>
+        <v>102370.49</v>
       </c>
       <c r="N13" t="n">
-        <v>115376.17</v>
+        <v>102370.49</v>
       </c>
       <c r="O13" t="n">
-        <v>149965.65</v>
+        <v>140881.99</v>
       </c>
       <c r="P13" t="n">
-        <v>900732.49</v>
+        <v>920307.22</v>
       </c>
       <c r="Q13" t="n">
-        <v>900732.49</v>
+        <v>920307.22</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>72335.94</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>329881.22</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>402217.17</v>
       </c>
       <c r="U13" t="n">
-        <v>900732.49</v>
+        <v>518090.06</v>
       </c>
       <c r="V13" t="n">
-        <v>900732.49</v>
+        <v>920307.22</v>
       </c>
       <c r="W13" t="n">
-        <v>900732.49</v>
+        <v>518090.06</v>
       </c>
     </row>
     <row r="14">
@@ -1464,43 +1464,43 @@
         <v>0.0532</v>
       </c>
       <c r="E14" t="n">
-        <v>4.496731305638313</v>
+        <v>4.160898435358346</v>
       </c>
       <c r="F14" t="n">
-        <v>-817014.13</v>
+        <v>-755988.77</v>
       </c>
       <c r="G14" t="n">
-        <v>1055466.6</v>
+        <v>1023209.84</v>
       </c>
       <c r="H14" t="n">
-        <v>238452.47</v>
+        <v>267221.07</v>
       </c>
       <c r="I14" t="n">
-        <v>12473.63</v>
+        <v>12390.22</v>
       </c>
       <c r="J14" t="n">
-        <v>23009.65770842694</v>
+        <v>22745.29360984699</v>
       </c>
       <c r="K14" t="n">
-        <v>23009.66</v>
+        <v>22745.29</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>125436.41</v>
+        <v>105932.1</v>
       </c>
       <c r="N14" t="n">
-        <v>125436.41</v>
+        <v>105932.1</v>
       </c>
       <c r="O14" t="n">
-        <v>160919.7</v>
+        <v>141067.61</v>
       </c>
       <c r="P14" t="n">
-        <v>74367.95</v>
+        <v>123130.63</v>
       </c>
       <c r="Q14" t="n">
-        <v>77532.77</v>
+        <v>126153.46</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1512,13 +1512,13 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>77532.77</v>
+        <v>126153.46</v>
       </c>
       <c r="V14" t="n">
-        <v>77532.77</v>
+        <v>126153.46</v>
       </c>
       <c r="W14" t="n">
-        <v>77532.77</v>
+        <v>126153.46</v>
       </c>
     </row>
     <row r="15">
@@ -1539,43 +1539,43 @@
         <v>0.0532</v>
       </c>
       <c r="E15" t="n">
-        <v>4.462218364970779</v>
+        <v>4.23726598863084</v>
       </c>
       <c r="F15" t="n">
-        <v>10162412.47</v>
+        <v>8461101.619999999</v>
       </c>
       <c r="G15" t="n">
-        <v>-9482168.65</v>
+        <v>-7961945.45</v>
       </c>
       <c r="H15" t="n">
-        <v>680243.8199999999</v>
+        <v>499156.17</v>
       </c>
       <c r="I15" t="n">
-        <v>29663.2</v>
+        <v>27167.87</v>
       </c>
       <c r="J15" t="n">
-        <v>23040.9564214907</v>
+        <v>23439.75368639317</v>
       </c>
       <c r="K15" t="n">
-        <v>23040.96</v>
+        <v>23439.75</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>122262.18</v>
+        <v>106719.48</v>
       </c>
       <c r="N15" t="n">
-        <v>122262.18</v>
+        <v>106719.48</v>
       </c>
       <c r="O15" t="n">
-        <v>174966.33</v>
+        <v>157327.1</v>
       </c>
       <c r="P15" t="n">
-        <v>505277.49</v>
+        <v>341829.07</v>
       </c>
       <c r="Q15" t="n">
-        <v>505277.49</v>
+        <v>341829.07</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -1587,13 +1587,13 @@
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>505277.49</v>
+        <v>341829.07</v>
       </c>
       <c r="V15" t="n">
-        <v>505277.49</v>
+        <v>341829.07</v>
       </c>
       <c r="W15" t="n">
-        <v>505277.49</v>
+        <v>341829.07</v>
       </c>
     </row>
     <row r="16">
@@ -1614,61 +1614,61 @@
         <v>0.0533</v>
       </c>
       <c r="E16" t="n">
-        <v>4.548256662970584</v>
+        <v>4.319441526751256</v>
       </c>
       <c r="F16" t="n">
-        <v>4515385.21</v>
+        <v>3981850.78</v>
       </c>
       <c r="G16" t="n">
-        <v>-4055466</v>
+        <v>-3549420.01</v>
       </c>
       <c r="H16" t="n">
-        <v>459919.22</v>
+        <v>432430.77</v>
       </c>
       <c r="I16" t="n">
-        <v>18120.47</v>
+        <v>15853.93</v>
       </c>
       <c r="J16" t="n">
-        <v>24491.00553623115</v>
+        <v>24684.15119403339</v>
       </c>
       <c r="K16" t="n">
-        <v>24491.01</v>
+        <v>24684.15</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>126348.81</v>
+        <v>110197.18</v>
       </c>
       <c r="N16" t="n">
-        <v>126348.81</v>
+        <v>110197.18</v>
       </c>
       <c r="O16" t="n">
-        <v>168960.28</v>
+        <v>150735.26</v>
       </c>
       <c r="P16" t="n">
-        <v>291497.01</v>
+        <v>281980.53</v>
       </c>
       <c r="Q16" t="n">
-        <v>290958.93</v>
+        <v>281695.51</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>81982.02</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>155967.26</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>237949.28</v>
       </c>
       <c r="U16" t="n">
-        <v>290958.93</v>
+        <v>43746.23</v>
       </c>
       <c r="V16" t="n">
-        <v>290958.93</v>
+        <v>281695.51</v>
       </c>
       <c r="W16" t="n">
-        <v>290958.93</v>
+        <v>43746.23</v>
       </c>
     </row>
     <row r="17">
@@ -1689,43 +1689,43 @@
         <v>0.0532</v>
       </c>
       <c r="E17" t="n">
-        <v>4.542796500599895</v>
+        <v>4.28305584662614</v>
       </c>
       <c r="F17" t="n">
-        <v>-2961512.53</v>
+        <v>-2332769.16</v>
       </c>
       <c r="G17" t="n">
-        <v>3241452.93</v>
+        <v>2462026.24</v>
       </c>
       <c r="H17" t="n">
-        <v>279940.4</v>
+        <v>129257.08</v>
       </c>
       <c r="I17" t="n">
-        <v>22318.44</v>
+        <v>24799.61</v>
       </c>
       <c r="J17" t="n">
-        <v>25774.72383318911</v>
+        <v>26324.84780952142</v>
       </c>
       <c r="K17" t="n">
-        <v>25774.72</v>
+        <v>26324.85</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>141459.22</v>
+        <v>121872.63</v>
       </c>
       <c r="N17" t="n">
-        <v>141459.22</v>
+        <v>121872.63</v>
       </c>
       <c r="O17" t="n">
-        <v>189552.39</v>
+        <v>172997.08</v>
       </c>
       <c r="P17" t="n">
-        <v>90336.85000000001</v>
+        <v>-43790.26</v>
       </c>
       <c r="Q17" t="n">
-        <v>90388.00999999999</v>
+        <v>-43740</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -1737,13 +1737,13 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>90388.00999999999</v>
+        <v>-43740</v>
       </c>
       <c r="V17" t="n">
-        <v>90388.00999999999</v>
+        <v>-43740</v>
       </c>
       <c r="W17" t="n">
-        <v>90388.00999999999</v>
+        <v>-43740</v>
       </c>
     </row>
     <row r="18">
@@ -1764,43 +1764,43 @@
         <v>0.0532</v>
       </c>
       <c r="E18" t="n">
-        <v>4.444485970021087</v>
+        <v>4.23501016408488</v>
       </c>
       <c r="F18" t="n">
-        <v>5454988.61</v>
+        <v>4854990.41</v>
       </c>
       <c r="G18" t="n">
-        <v>-4946596.47</v>
+        <v>-4483908.27</v>
       </c>
       <c r="H18" t="n">
-        <v>508392.14</v>
+        <v>371082.14</v>
       </c>
       <c r="I18" t="n">
-        <v>14332.59</v>
+        <v>13455.48</v>
       </c>
       <c r="J18" t="n">
-        <v>24257.79367043497</v>
+        <v>25111.94152888906</v>
       </c>
       <c r="K18" t="n">
-        <v>24257.79</v>
+        <v>25111.94</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>138645.56</v>
+        <v>120705.52</v>
       </c>
       <c r="N18" t="n">
-        <v>138645.56</v>
+        <v>120705.52</v>
       </c>
       <c r="O18" t="n">
-        <v>177235.94</v>
+        <v>159272.94</v>
       </c>
       <c r="P18" t="n">
-        <v>331156.2</v>
+        <v>211809.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>331156.2</v>
+        <v>211809.2</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -1812,13 +1812,13 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>331156.2</v>
+        <v>211809.2</v>
       </c>
       <c r="V18" t="n">
-        <v>331156.2</v>
+        <v>211809.2</v>
       </c>
       <c r="W18" t="n">
-        <v>331156.2</v>
+        <v>211809.2</v>
       </c>
     </row>
     <row r="19">
@@ -1839,61 +1839,61 @@
         <v>0.0532</v>
       </c>
       <c r="E19" t="n">
-        <v>4.521355755412176</v>
+        <v>4.306400725633772</v>
       </c>
       <c r="F19" t="n">
-        <v>2706321.62</v>
+        <v>2014039.84</v>
       </c>
       <c r="G19" t="n">
-        <v>-2295663.86</v>
+        <v>-1707414.05</v>
       </c>
       <c r="H19" t="n">
-        <v>410657.76</v>
+        <v>306625.78</v>
       </c>
       <c r="I19" t="n">
-        <v>9437.540000000001</v>
+        <v>9126.6</v>
       </c>
       <c r="J19" t="n">
-        <v>21776.16099907778</v>
+        <v>22408.21992674831</v>
       </c>
       <c r="K19" t="n">
-        <v>21776.16</v>
+        <v>22408.22</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>123215.44</v>
+        <v>106615.53</v>
       </c>
       <c r="N19" t="n">
-        <v>123215.44</v>
+        <v>106615.53</v>
       </c>
       <c r="O19" t="n">
-        <v>154429.14</v>
+        <v>138150.35</v>
       </c>
       <c r="P19" t="n">
-        <v>256371.01</v>
+        <v>168672.92</v>
       </c>
       <c r="Q19" t="n">
-        <v>256228.62</v>
+        <v>168475.43</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>86422.88</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>90276.47</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>176699.35</v>
       </c>
       <c r="U19" t="n">
-        <v>256228.62</v>
+        <v>-8223.92</v>
       </c>
       <c r="V19" t="n">
-        <v>256228.62</v>
+        <v>168475.43</v>
       </c>
       <c r="W19" t="n">
-        <v>256228.62</v>
+        <v>-8223.92</v>
       </c>
     </row>
     <row r="20">
@@ -1914,43 +1914,43 @@
         <v>0.0532</v>
       </c>
       <c r="E20" t="n">
-        <v>4.426572891877691</v>
+        <v>4.232871245974343</v>
       </c>
       <c r="F20" t="n">
-        <v>767981.64</v>
+        <v>953759.3100000001</v>
       </c>
       <c r="G20" t="n">
-        <v>-331963.75</v>
+        <v>-627575.33</v>
       </c>
       <c r="H20" t="n">
-        <v>436017.88</v>
+        <v>326183.98</v>
       </c>
       <c r="I20" t="n">
-        <v>28844.15</v>
+        <v>26039.84</v>
       </c>
       <c r="J20" t="n">
-        <v>25498.30310047942</v>
+        <v>26254.90954906872</v>
       </c>
       <c r="K20" t="n">
-        <v>25498.3</v>
+        <v>26254.91</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>139590.3</v>
+        <v>120448.81</v>
       </c>
       <c r="N20" t="n">
-        <v>139590.3</v>
+        <v>120448.81</v>
       </c>
       <c r="O20" t="n">
-        <v>193932.76</v>
+        <v>172743.56</v>
       </c>
       <c r="P20" t="n">
-        <v>242738.96</v>
+        <v>154073.69</v>
       </c>
       <c r="Q20" t="n">
-        <v>242085.13</v>
+        <v>153440.41</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -1962,13 +1962,13 @@
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>242085.13</v>
+        <v>153440.41</v>
       </c>
       <c r="V20" t="n">
-        <v>242085.13</v>
+        <v>153440.41</v>
       </c>
       <c r="W20" t="n">
-        <v>242085.13</v>
+        <v>153440.41</v>
       </c>
     </row>
     <row r="21">
@@ -1989,43 +1989,43 @@
         <v>0.0532</v>
       </c>
       <c r="E21" t="n">
-        <v>4.363798757652462</v>
+        <v>4.175523178337027</v>
       </c>
       <c r="F21" t="n">
-        <v>-1667540.74</v>
+        <v>-1410585.42</v>
       </c>
       <c r="G21" t="n">
-        <v>2287334.71</v>
+        <v>1933093.57</v>
       </c>
       <c r="H21" t="n">
-        <v>619793.97</v>
+        <v>522508.15</v>
       </c>
       <c r="I21" t="n">
-        <v>32008.56</v>
+        <v>28532.65</v>
       </c>
       <c r="J21" t="n">
-        <v>24152.96373830043</v>
+        <v>24741.98697499681</v>
       </c>
       <c r="K21" t="n">
-        <v>24152.96</v>
+        <v>24741.99</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>140299.27</v>
+        <v>121029</v>
       </c>
       <c r="N21" t="n">
-        <v>140299.27</v>
+        <v>121029</v>
       </c>
       <c r="O21" t="n">
-        <v>196460.8</v>
+        <v>174303.64</v>
       </c>
       <c r="P21" t="n">
-        <v>423333.18</v>
+        <v>348204.51</v>
       </c>
       <c r="Q21" t="n">
-        <v>423333.18</v>
+        <v>348204.51</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2037,13 +2037,13 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>423333.18</v>
+        <v>348204.51</v>
       </c>
       <c r="V21" t="n">
-        <v>423333.18</v>
+        <v>348204.51</v>
       </c>
       <c r="W21" t="n">
-        <v>423333.18</v>
+        <v>348204.51</v>
       </c>
     </row>
     <row r="22">
@@ -2064,61 +2064,61 @@
         <v>0.0483</v>
       </c>
       <c r="E22" t="n">
-        <v>4.486639914588435</v>
+        <v>4.300151056408744</v>
       </c>
       <c r="F22" t="n">
-        <v>3972696.69</v>
+        <v>3515015.79</v>
       </c>
       <c r="G22" t="n">
-        <v>-4207529.14</v>
+        <v>-3756284.77</v>
       </c>
       <c r="H22" t="n">
-        <v>-234832.45</v>
+        <v>-241268.99</v>
       </c>
       <c r="I22" t="n">
-        <v>47518.96</v>
+        <v>42357.16</v>
       </c>
       <c r="J22" t="n">
-        <v>26791.58078786265</v>
+        <v>26750.84479658073</v>
       </c>
       <c r="K22" t="n">
-        <v>26791.58</v>
+        <v>26750.84</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>127873.27</v>
+        <v>110509.28</v>
       </c>
       <c r="N22" t="n">
-        <v>127873.27</v>
+        <v>110509.28</v>
       </c>
       <c r="O22" t="n">
-        <v>202183.81</v>
+        <v>179617.29</v>
       </c>
       <c r="P22" t="n">
-        <v>-436520.65</v>
+        <v>-420499.42</v>
       </c>
       <c r="Q22" t="n">
-        <v>-437016.26</v>
+        <v>-420886.27</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>88993.32000000001</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>8072.55</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>97065.87</v>
       </c>
       <c r="U22" t="n">
-        <v>-437016.26</v>
+        <v>-517952.14</v>
       </c>
       <c r="V22" t="n">
-        <v>-437016.26</v>
+        <v>-420886.27</v>
       </c>
       <c r="W22" t="n">
-        <v>-437016.26</v>
+        <v>-517952.14</v>
       </c>
     </row>
     <row r="23">
@@ -2139,43 +2139,43 @@
         <v>0.0483</v>
       </c>
       <c r="E23" t="n">
-        <v>4.215495283604056</v>
+        <v>4.068699598767902</v>
       </c>
       <c r="F23" t="n">
-        <v>138813.32</v>
+        <v>180688.68</v>
       </c>
       <c r="G23" t="n">
-        <v>412896.6</v>
+        <v>294507.04</v>
       </c>
       <c r="H23" t="n">
-        <v>551709.92</v>
+        <v>475195.72</v>
       </c>
       <c r="I23" t="n">
-        <v>26176.16</v>
+        <v>24644.97</v>
       </c>
       <c r="J23" t="n">
-        <v>59775.86802034196</v>
+        <v>56705.4632854517</v>
       </c>
       <c r="K23" t="n">
-        <v>59775.87</v>
+        <v>56705.46</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>121644.02</v>
+        <v>105981.82</v>
       </c>
       <c r="N23" t="n">
-        <v>121644.02</v>
+        <v>105981.82</v>
       </c>
       <c r="O23" t="n">
-        <v>207596.05</v>
+        <v>187332.26</v>
       </c>
       <c r="P23" t="n">
-        <v>344586.8</v>
+        <v>288320.98</v>
       </c>
       <c r="Q23" t="n">
-        <v>344113.87</v>
+        <v>287863.47</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -2187,13 +2187,13 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>344113.87</v>
+        <v>287863.47</v>
       </c>
       <c r="V23" t="n">
-        <v>344113.87</v>
+        <v>287863.47</v>
       </c>
       <c r="W23" t="n">
-        <v>344113.87</v>
+        <v>287863.47</v>
       </c>
     </row>
     <row r="24">
@@ -2214,43 +2214,43 @@
         <v>0.0458</v>
       </c>
       <c r="E24" t="n">
-        <v>4.175718448933872</v>
+        <v>4.037809810790291</v>
       </c>
       <c r="F24" t="n">
-        <v>5791134.34</v>
+        <v>4893396.11</v>
       </c>
       <c r="G24" t="n">
-        <v>-5314328.12</v>
+        <v>-4544238.14</v>
       </c>
       <c r="H24" t="n">
-        <v>476806.22</v>
+        <v>349157.96</v>
       </c>
       <c r="I24" t="n">
-        <v>36183.78</v>
+        <v>32714.8</v>
       </c>
       <c r="J24" t="n">
-        <v>56511.55639966222</v>
+        <v>53596.15558076301</v>
       </c>
       <c r="K24" t="n">
-        <v>56511.56</v>
+        <v>53596.16</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>101132.55</v>
+        <v>88162.3</v>
       </c>
       <c r="N24" t="n">
-        <v>101132.55</v>
+        <v>88162.3</v>
       </c>
       <c r="O24" t="n">
-        <v>193827.89</v>
+        <v>174473.26</v>
       </c>
       <c r="P24" t="n">
-        <v>283420.52</v>
+        <v>175162.46</v>
       </c>
       <c r="Q24" t="n">
-        <v>282978.33</v>
+        <v>174684.71</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -2262,13 +2262,13 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>282978.33</v>
+        <v>174684.71</v>
       </c>
       <c r="V24" t="n">
-        <v>282978.33</v>
+        <v>174684.71</v>
       </c>
       <c r="W24" t="n">
-        <v>282978.33</v>
+        <v>174684.71</v>
       </c>
     </row>
     <row r="25">
@@ -2289,61 +2289,61 @@
         <v>0.0433</v>
       </c>
       <c r="E25" t="n">
-        <v>4.121338594128017</v>
+        <v>3.999301861018169</v>
       </c>
       <c r="F25" t="n">
-        <v>181577.78</v>
+        <v>47334.2</v>
       </c>
       <c r="G25" t="n">
-        <v>940256.71</v>
+        <v>963214.46</v>
       </c>
       <c r="H25" t="n">
-        <v>1121834.49</v>
+        <v>1010548.66</v>
       </c>
       <c r="I25" t="n">
-        <v>24873.21</v>
+        <v>22338.27</v>
       </c>
       <c r="J25" t="n">
-        <v>60855.95770426944</v>
+        <v>57039.72962825617</v>
       </c>
       <c r="K25" t="n">
-        <v>60855.96</v>
+        <v>57039.73</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>103321.14</v>
+        <v>90340.52</v>
       </c>
       <c r="N25" t="n">
-        <v>103321.14</v>
+        <v>90340.52</v>
       </c>
       <c r="O25" t="n">
-        <v>189050.3</v>
+        <v>169718.52</v>
       </c>
       <c r="P25" t="n">
-        <v>934655.77</v>
+        <v>842668.62</v>
       </c>
       <c r="Q25" t="n">
-        <v>932784.1899999999</v>
+        <v>840830.14</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>89223.17</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>216604.61</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>305827.78</v>
       </c>
       <c r="U25" t="n">
-        <v>932784.1899999999</v>
+        <v>535002.37</v>
       </c>
       <c r="V25" t="n">
-        <v>932784.1899999999</v>
+        <v>840830.14</v>
       </c>
       <c r="W25" t="n">
-        <v>932784.1899999999</v>
+        <v>535002.37</v>
       </c>
     </row>
     <row r="26">
@@ -2364,43 +2364,43 @@
         <v>0.0433</v>
       </c>
       <c r="E26" t="n">
-        <v>4.137489713183122</v>
+        <v>4.020764360631094</v>
       </c>
       <c r="F26" t="n">
-        <v>1892946.56</v>
+        <v>1716784.79</v>
       </c>
       <c r="G26" t="n">
-        <v>-906208.83</v>
+        <v>-808651.22</v>
       </c>
       <c r="H26" t="n">
-        <v>986737.73</v>
+        <v>908133.5600000001</v>
       </c>
       <c r="I26" t="n">
-        <v>30682.58</v>
+        <v>27919.69</v>
       </c>
       <c r="J26" t="n">
-        <v>62964.43117681984</v>
+        <v>57866.29971923039</v>
       </c>
       <c r="K26" t="n">
-        <v>62964.43</v>
+        <v>57866.3</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>101823.36</v>
+        <v>89103.17</v>
       </c>
       <c r="N26" t="n">
-        <v>101823.36</v>
+        <v>89103.17</v>
       </c>
       <c r="O26" t="n">
-        <v>195470.38</v>
+        <v>174889.16</v>
       </c>
       <c r="P26" t="n">
-        <v>792196.49</v>
+        <v>734197.84</v>
       </c>
       <c r="Q26" t="n">
-        <v>791267.36</v>
+        <v>733244.4</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -2412,13 +2412,13 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>791267.36</v>
+        <v>733244.4</v>
       </c>
       <c r="V26" t="n">
-        <v>791267.36</v>
+        <v>733244.4</v>
       </c>
       <c r="W26" t="n">
-        <v>791267.36</v>
+        <v>733244.4</v>
       </c>
     </row>
     <row r="27">
@@ -2439,43 +2439,43 @@
         <v>0.0433</v>
       </c>
       <c r="E27" t="n">
-        <v>4.155341199146508</v>
+        <v>4.067675932349523</v>
       </c>
       <c r="F27" t="n">
-        <v>-4232908.25</v>
+        <v>-3503954.84</v>
       </c>
       <c r="G27" t="n">
-        <v>4610498.99</v>
+        <v>3738504.43</v>
       </c>
       <c r="H27" t="n">
-        <v>377590.74</v>
+        <v>234549.6</v>
       </c>
       <c r="I27" t="n">
-        <v>30537.96</v>
+        <v>28075.09</v>
       </c>
       <c r="J27" t="n">
-        <v>60691.19478047488</v>
+        <v>56390.23091561231</v>
       </c>
       <c r="K27" t="n">
-        <v>60691.19</v>
+        <v>56390.23</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>97427.12</v>
+        <v>85887.13</v>
       </c>
       <c r="N27" t="n">
-        <v>97427.12</v>
+        <v>85887.13</v>
       </c>
       <c r="O27" t="n">
-        <v>188656.28</v>
+        <v>170352.45</v>
       </c>
       <c r="P27" t="n">
-        <v>188928.73</v>
+        <v>64179</v>
       </c>
       <c r="Q27" t="n">
-        <v>188934.46</v>
+        <v>64197.15</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -2487,13 +2487,13 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>188934.46</v>
+        <v>64197.15</v>
       </c>
       <c r="V27" t="n">
-        <v>188934.46</v>
+        <v>64197.15</v>
       </c>
       <c r="W27" t="n">
-        <v>188934.46</v>
+        <v>64197.15</v>
       </c>
     </row>
     <row r="28">
@@ -2514,61 +2514,61 @@
         <v>0.0433</v>
       </c>
       <c r="E28" t="n">
-        <v>4.090861249015584</v>
+        <v>4.000819403307661</v>
       </c>
       <c r="F28" t="n">
-        <v>-5659232.71</v>
+        <v>-4845299.68</v>
       </c>
       <c r="G28" t="n">
-        <v>7496497.58</v>
+        <v>6500678.84</v>
       </c>
       <c r="H28" t="n">
-        <v>1837264.87</v>
+        <v>1655379.16</v>
       </c>
       <c r="I28" t="n">
-        <v>30681.67</v>
+        <v>28619.35</v>
       </c>
       <c r="J28" t="n">
-        <v>69841.78269400471</v>
+        <v>66137.51888691494</v>
       </c>
       <c r="K28" t="n">
-        <v>69841.78</v>
+        <v>66137.52</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>110255.22</v>
+        <v>96914.46000000001</v>
       </c>
       <c r="N28" t="n">
-        <v>110255.22</v>
+        <v>96914.46000000001</v>
       </c>
       <c r="O28" t="n">
-        <v>210778.67</v>
+        <v>191671.33</v>
       </c>
       <c r="P28" t="n">
-        <v>1627028.66</v>
+        <v>1463840</v>
       </c>
       <c r="Q28" t="n">
-        <v>1626486.2</v>
+        <v>1463707.83</v>
       </c>
       <c r="R28" t="n">
-        <v>49726.48</v>
+        <v>95390.55</v>
       </c>
       <c r="S28" t="n">
-        <v>161578.85</v>
+        <v>356073.95</v>
       </c>
       <c r="T28" t="n">
-        <v>211305.33</v>
+        <v>451464.5</v>
       </c>
       <c r="U28" t="n">
-        <v>1415180.87</v>
+        <v>1012243.33</v>
       </c>
       <c r="V28" t="n">
-        <v>1626486.2</v>
+        <v>1463707.83</v>
       </c>
       <c r="W28" t="n">
-        <v>1415180.87</v>
+        <v>1012243.33</v>
       </c>
     </row>
     <row r="29">
@@ -2589,43 +2589,43 @@
         <v>0.0433</v>
       </c>
       <c r="E29" t="n">
-        <v>4.236666937754265</v>
+        <v>4.155237008808432</v>
       </c>
       <c r="F29" t="n">
-        <v>2790749.06</v>
+        <v>2894817.5</v>
       </c>
       <c r="G29" t="n">
-        <v>-1000868.5</v>
+        <v>-1294862.39</v>
       </c>
       <c r="H29" t="n">
-        <v>1789880.57</v>
+        <v>1599955.11</v>
       </c>
       <c r="I29" t="n">
-        <v>53706.62</v>
+        <v>49036.9</v>
       </c>
       <c r="J29" t="n">
-        <v>83676.82151790475</v>
+        <v>81816.61745331844</v>
       </c>
       <c r="K29" t="n">
-        <v>83676.82000000001</v>
+        <v>81816.62</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>127133.9</v>
+        <v>112517.3</v>
       </c>
       <c r="N29" t="n">
-        <v>127133.9</v>
+        <v>112517.3</v>
       </c>
       <c r="O29" t="n">
-        <v>264517.33</v>
+        <v>243370.82</v>
       </c>
       <c r="P29" t="n">
-        <v>1524956.47</v>
+        <v>1356077.08</v>
       </c>
       <c r="Q29" t="n">
-        <v>1525363.23</v>
+        <v>1356584.29</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -2637,13 +2637,13 @@
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1525363.23</v>
+        <v>1356584.29</v>
       </c>
       <c r="V29" t="n">
-        <v>1525363.23</v>
+        <v>1356584.29</v>
       </c>
       <c r="W29" t="n">
-        <v>1525363.23</v>
+        <v>1356584.29</v>
       </c>
     </row>
     <row r="30">
@@ -2664,43 +2664,43 @@
         <v>0.0433</v>
       </c>
       <c r="E30" t="n">
-        <v>4.363814397757752</v>
+        <v>4.292409812557828</v>
       </c>
       <c r="F30" t="n">
-        <v>11479082.61</v>
+        <v>10018446.98</v>
       </c>
       <c r="G30" t="n">
-        <v>-11180837.31</v>
+        <v>-9764412.52</v>
       </c>
       <c r="H30" t="n">
-        <v>298245.3</v>
+        <v>254034.47</v>
       </c>
       <c r="I30" t="n">
-        <v>43914.33</v>
+        <v>39825.84</v>
       </c>
       <c r="J30" t="n">
-        <v>95038.97805236513</v>
+        <v>89510.63215673738</v>
       </c>
       <c r="K30" t="n">
-        <v>95038.98</v>
+        <v>89510.63</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>134261.49</v>
+        <v>119166.35</v>
       </c>
       <c r="N30" t="n">
-        <v>134261.49</v>
+        <v>119166.35</v>
       </c>
       <c r="O30" t="n">
-        <v>273214.8</v>
+        <v>248502.82</v>
       </c>
       <c r="P30" t="n">
-        <v>24989.21</v>
+        <v>5642.25</v>
       </c>
       <c r="Q30" t="n">
-        <v>25030.49</v>
+        <v>5531.64</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -2712,13 +2712,13 @@
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>25030.49</v>
+        <v>5531.64</v>
       </c>
       <c r="V30" t="n">
-        <v>25030.49</v>
+        <v>5531.64</v>
       </c>
       <c r="W30" t="n">
-        <v>25030.49</v>
+        <v>5531.64</v>
       </c>
     </row>
     <row r="31">
@@ -2739,61 +2739,61 @@
         <v>0.0433</v>
       </c>
       <c r="E31" t="n">
-        <v>4.408082645713115</v>
+        <v>4.337311205890681</v>
       </c>
       <c r="F31" t="n">
-        <v>7203948.29</v>
+        <v>6219009.94</v>
       </c>
       <c r="G31" t="n">
-        <v>-6874363.66</v>
+        <v>-5875259.41</v>
       </c>
       <c r="H31" t="n">
-        <v>329584.62</v>
+        <v>343750.53</v>
       </c>
       <c r="I31" t="n">
-        <v>29620.42</v>
+        <v>26110.49</v>
       </c>
       <c r="J31" t="n">
-        <v>95558.18968603574</v>
+        <v>87997.70040974021</v>
       </c>
       <c r="K31" t="n">
-        <v>95558.19</v>
+        <v>87997.7</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>129553.09</v>
+        <v>115115.06</v>
       </c>
       <c r="N31" t="n">
-        <v>129553.09</v>
+        <v>115115.06</v>
       </c>
       <c r="O31" t="n">
-        <v>254731.7</v>
+        <v>229223.25</v>
       </c>
       <c r="P31" t="n">
-        <v>73913.24000000001</v>
+        <v>114242.97</v>
       </c>
       <c r="Q31" t="n">
-        <v>74852.92</v>
+        <v>114527.28</v>
       </c>
       <c r="R31" t="n">
-        <v>54103.88</v>
+        <v>106008</v>
       </c>
       <c r="S31" t="n">
-        <v>126633.47</v>
+        <v>205815.18</v>
       </c>
       <c r="T31" t="n">
-        <v>180737.34</v>
+        <v>311823.17</v>
       </c>
       <c r="U31" t="n">
-        <v>-105884.42</v>
+        <v>-197295.89</v>
       </c>
       <c r="V31" t="n">
-        <v>74852.92</v>
+        <v>114527.28</v>
       </c>
       <c r="W31" t="n">
-        <v>-105884.42</v>
+        <v>-197295.89</v>
       </c>
     </row>
     <row r="32">
@@ -2814,43 +2814,43 @@
         <v>0.0433</v>
       </c>
       <c r="E32" t="n">
-        <v>4.297217936857737</v>
+        <v>4.243653152040969</v>
       </c>
       <c r="F32" t="n">
-        <v>5095142.2</v>
+        <v>4082108.32</v>
       </c>
       <c r="G32" t="n">
-        <v>-4517555.05</v>
+        <v>-3523925.75</v>
       </c>
       <c r="H32" t="n">
-        <v>577587.16</v>
+        <v>558182.5699999999</v>
       </c>
       <c r="I32" t="n">
-        <v>29371</v>
+        <v>27263.61</v>
       </c>
       <c r="J32" t="n">
-        <v>118008.8512909473</v>
+        <v>107410.6345902989</v>
       </c>
       <c r="K32" t="n">
-        <v>118008.85</v>
+        <v>107410.63</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>139638.35</v>
+        <v>125134.09</v>
       </c>
       <c r="N32" t="n">
-        <v>139638.35</v>
+        <v>125134.09</v>
       </c>
       <c r="O32" t="n">
-        <v>287018.19</v>
+        <v>259808.33</v>
       </c>
       <c r="P32" t="n">
-        <v>290970.96</v>
+        <v>298737.41</v>
       </c>
       <c r="Q32" t="n">
-        <v>290568.96</v>
+        <v>298374.24</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -2862,13 +2862,13 @@
         <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>290568.96</v>
+        <v>298374.24</v>
       </c>
       <c r="V32" t="n">
-        <v>290568.96</v>
+        <v>298374.24</v>
       </c>
       <c r="W32" t="n">
-        <v>290568.96</v>
+        <v>298374.24</v>
       </c>
     </row>
     <row r="33">
@@ -2889,43 +2889,43 @@
         <v>0.0433</v>
       </c>
       <c r="E33" t="n">
-        <v>4.344970811214985</v>
+        <v>4.314163112947152</v>
       </c>
       <c r="F33" t="n">
-        <v>1030043.33</v>
+        <v>1308117.89</v>
       </c>
       <c r="G33" t="n">
-        <v>-438766.11</v>
+        <v>-793416.67</v>
       </c>
       <c r="H33" t="n">
-        <v>591277.21</v>
+        <v>514701.23</v>
       </c>
       <c r="I33" t="n">
-        <v>44919.02</v>
+        <v>41153.21</v>
       </c>
       <c r="J33" t="n">
-        <v>139057.3941616204</v>
+        <v>121680.6973342472</v>
       </c>
       <c r="K33" t="n">
-        <v>139057.39</v>
+        <v>121680.7</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>133537.45</v>
+        <v>120597.51</v>
       </c>
       <c r="N33" t="n">
-        <v>133537.45</v>
+        <v>120597.51</v>
       </c>
       <c r="O33" t="n">
-        <v>317513.87</v>
+        <v>283431.42</v>
       </c>
       <c r="P33" t="n">
-        <v>271767.73</v>
+        <v>229440.52</v>
       </c>
       <c r="Q33" t="n">
-        <v>273763.35</v>
+        <v>231269.81</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>273763.35</v>
+        <v>231269.81</v>
       </c>
       <c r="V33" t="n">
-        <v>273763.35</v>
+        <v>231269.81</v>
       </c>
       <c r="W33" t="n">
-        <v>273763.35</v>
+        <v>231269.81</v>
       </c>
     </row>
     <row r="34">
@@ -2964,61 +2964,61 @@
         <v>0.0409</v>
       </c>
       <c r="E34" t="n">
-        <v>4.42954398510511</v>
+        <v>4.424262340213177</v>
       </c>
       <c r="F34" t="n">
-        <v>8685515.630000001</v>
+        <v>8428167.15</v>
       </c>
       <c r="G34" t="n">
-        <v>-8464296.300000001</v>
+        <v>-8273395.92</v>
       </c>
       <c r="H34" t="n">
-        <v>221219.33</v>
+        <v>154771.23</v>
       </c>
       <c r="I34" t="n">
-        <v>43220.46</v>
+        <v>40769.83</v>
       </c>
       <c r="J34" t="n">
-        <v>160403.0118349085</v>
+        <v>139577.0344012068</v>
       </c>
       <c r="K34" t="n">
-        <v>160403.01</v>
+        <v>139577.03</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>135288.18</v>
+        <v>123342.93</v>
       </c>
       <c r="N34" t="n">
-        <v>135288.18</v>
+        <v>123342.93</v>
       </c>
       <c r="O34" t="n">
-        <v>338911.64</v>
+        <v>303689.8</v>
       </c>
       <c r="P34" t="n">
-        <v>-111571.62</v>
+        <v>-143145.54</v>
       </c>
       <c r="Q34" t="n">
-        <v>-117692.32</v>
+        <v>-148918.56</v>
       </c>
       <c r="R34" t="n">
-        <v>57534.55</v>
+        <v>112145.01</v>
       </c>
       <c r="S34" t="n">
-        <v>30464.21</v>
+        <v>38627</v>
       </c>
       <c r="T34" t="n">
-        <v>87998.75999999999</v>
+        <v>150772.01</v>
       </c>
       <c r="U34" t="n">
-        <v>-205691.08</v>
+        <v>-299690.57</v>
       </c>
       <c r="V34" t="n">
-        <v>-117692.32</v>
+        <v>-148918.56</v>
       </c>
       <c r="W34" t="n">
-        <v>-205691.08</v>
+        <v>-299690.57</v>
       </c>
     </row>
     <row r="35">
@@ -3039,43 +3039,43 @@
         <v>0.0386</v>
       </c>
       <c r="E35" t="n">
-        <v>4.426901975209142</v>
+        <v>4.439295723762534</v>
       </c>
       <c r="F35" t="n">
-        <v>4695393.16</v>
+        <v>3535848.32</v>
       </c>
       <c r="G35" t="n">
-        <v>-3679490.96</v>
+        <v>-2630683.7</v>
       </c>
       <c r="H35" t="n">
-        <v>1015902.21</v>
+        <v>905164.61</v>
       </c>
       <c r="I35" t="n">
-        <v>45056.16</v>
+        <v>41508.31</v>
       </c>
       <c r="J35" t="n">
-        <v>178750.1068107546</v>
+        <v>158390.7621401346</v>
       </c>
       <c r="K35" t="n">
-        <v>178750.11</v>
+        <v>158390.76</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>142812.25</v>
+        <v>131030.05</v>
       </c>
       <c r="N35" t="n">
-        <v>142812.25</v>
+        <v>131030.05</v>
       </c>
       <c r="O35" t="n">
-        <v>366618.52</v>
+        <v>330929.12</v>
       </c>
       <c r="P35" t="n">
-        <v>648975.7</v>
+        <v>573869.51</v>
       </c>
       <c r="Q35" t="n">
-        <v>649283.6899999999</v>
+        <v>574235.49</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -3087,13 +3087,13 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>649283.6899999999</v>
+        <v>574235.49</v>
       </c>
       <c r="V35" t="n">
-        <v>649283.6899999999</v>
+        <v>574235.49</v>
       </c>
       <c r="W35" t="n">
-        <v>649283.6899999999</v>
+        <v>574235.49</v>
       </c>
     </row>
     <row r="36">
@@ -3114,43 +3114,43 @@
         <v>0.0388</v>
       </c>
       <c r="E36" t="n">
-        <v>4.344185305810045</v>
+        <v>4.375956524981069</v>
       </c>
       <c r="F36" t="n">
-        <v>-6633788.74</v>
+        <v>-6020348.23</v>
       </c>
       <c r="G36" t="n">
-        <v>6695326.9</v>
+        <v>6034160.92</v>
       </c>
       <c r="H36" t="n">
-        <v>61538.16</v>
+        <v>13812.69</v>
       </c>
       <c r="I36" t="n">
-        <v>62925.21</v>
+        <v>57831.1</v>
       </c>
       <c r="J36" t="n">
-        <v>150432.8249113848</v>
+        <v>132244.5458945951</v>
       </c>
       <c r="K36" t="n">
-        <v>150432.82</v>
+        <v>132244.55</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>111024.93</v>
+        <v>102333</v>
       </c>
       <c r="N36" t="n">
-        <v>111024.93</v>
+        <v>102333</v>
       </c>
       <c r="O36" t="n">
-        <v>324382.96</v>
+        <v>292408.65</v>
       </c>
       <c r="P36" t="n">
-        <v>-261987.01</v>
+        <v>-277966.74</v>
       </c>
       <c r="Q36" t="n">
-        <v>-262844.8</v>
+        <v>-278595.96</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -3162,13 +3162,13 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>-262844.8</v>
+        <v>-278595.96</v>
       </c>
       <c r="V36" t="n">
-        <v>-262844.8</v>
+        <v>-278595.96</v>
       </c>
       <c r="W36" t="n">
-        <v>-262844.8</v>
+        <v>-278595.96</v>
       </c>
     </row>
     <row r="37">
@@ -3189,61 +3189,61 @@
         <v>0.0365</v>
       </c>
       <c r="E37" t="n">
-        <v>4.423680303176043</v>
+        <v>4.48874428325304</v>
       </c>
       <c r="F37" t="n">
-        <v>-1374943.16</v>
+        <v>-1432409.34</v>
       </c>
       <c r="G37" t="n">
-        <v>2580772.76</v>
+        <v>2565550.75</v>
       </c>
       <c r="H37" t="n">
-        <v>1205829.6</v>
+        <v>1133141.4</v>
       </c>
       <c r="I37" t="n">
-        <v>27240.89</v>
+        <v>26347.25</v>
       </c>
       <c r="J37" t="n">
-        <v>182891.2053595921</v>
+        <v>159409.3399601358</v>
       </c>
       <c r="K37" t="n">
-        <v>182891.21</v>
+        <v>159409.34</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>129025.77</v>
+        <v>120314.81</v>
       </c>
       <c r="N37" t="n">
-        <v>129025.77</v>
+        <v>120314.81</v>
       </c>
       <c r="O37" t="n">
-        <v>339157.86</v>
+        <v>306071.4</v>
       </c>
       <c r="P37" t="n">
-        <v>867701.3100000001</v>
+        <v>828170.92</v>
       </c>
       <c r="Q37" t="n">
-        <v>866671.75</v>
+        <v>827070</v>
       </c>
       <c r="R37" t="n">
-        <v>58359.87</v>
+        <v>113296.79</v>
       </c>
       <c r="S37" t="n">
-        <v>170825.28</v>
+        <v>146794.28</v>
       </c>
       <c r="T37" t="n">
-        <v>229185.15</v>
+        <v>260091.07</v>
       </c>
       <c r="U37" t="n">
-        <v>637486.59</v>
+        <v>566978.9399999999</v>
       </c>
       <c r="V37" t="n">
-        <v>866671.75</v>
+        <v>827070</v>
       </c>
       <c r="W37" t="n">
-        <v>637486.59</v>
+        <v>566978.9399999999</v>
       </c>
     </row>
     <row r="38">
@@ -3264,43 +3264,43 @@
         <v>0.0363</v>
       </c>
       <c r="E38" t="n">
-        <v>4.500010619906295</v>
+        <v>4.578251486178021</v>
       </c>
       <c r="F38" t="n">
-        <v>1413650.56</v>
+        <v>1119726.71</v>
       </c>
       <c r="G38" t="n">
-        <v>-485014.29</v>
+        <v>-274719.49</v>
       </c>
       <c r="H38" t="n">
-        <v>928636.27</v>
+        <v>845007.22</v>
       </c>
       <c r="I38" t="n">
-        <v>47387.28</v>
+        <v>43970.55</v>
       </c>
       <c r="J38" t="n">
-        <v>179259.6162691689</v>
+        <v>156989.4925524802</v>
       </c>
       <c r="K38" t="n">
-        <v>179259.62</v>
+        <v>156989.49</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>120711.47</v>
+        <v>113032.13</v>
       </c>
       <c r="N38" t="n">
-        <v>120711.47</v>
+        <v>113032.13</v>
       </c>
       <c r="O38" t="n">
-        <v>347358.36</v>
+        <v>313992.18</v>
       </c>
       <c r="P38" t="n">
-        <v>581733.13</v>
+        <v>531603.34</v>
       </c>
       <c r="Q38" t="n">
-        <v>581277.9</v>
+        <v>531015.05</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -3312,13 +3312,13 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>581277.9</v>
+        <v>531015.05</v>
       </c>
       <c r="V38" t="n">
-        <v>581277.9</v>
+        <v>531015.05</v>
       </c>
       <c r="W38" t="n">
-        <v>581277.9</v>
+        <v>531015.05</v>
       </c>
     </row>
     <row r="39">
@@ -3339,43 +3339,43 @@
         <v>0.0363</v>
       </c>
       <c r="E39" t="n">
-        <v>4.417214289881142</v>
+        <v>4.519924205026048</v>
       </c>
       <c r="F39" t="n">
-        <v>-4558647.76</v>
+        <v>-3907411.25</v>
       </c>
       <c r="G39" t="n">
-        <v>7255317.48</v>
+        <v>6406182.98</v>
       </c>
       <c r="H39" t="n">
-        <v>2696669.72</v>
+        <v>2498771.72</v>
       </c>
       <c r="I39" t="n">
-        <v>46361.17</v>
+        <v>46156.18</v>
       </c>
       <c r="J39" t="n">
-        <v>190487.7829969968</v>
+        <v>168931.0708225083</v>
       </c>
       <c r="K39" t="n">
-        <v>190487.78</v>
+        <v>168931.07</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>117685.29</v>
+        <v>111333.83</v>
       </c>
       <c r="N39" t="n">
-        <v>117685.29</v>
+        <v>111333.83</v>
       </c>
       <c r="O39" t="n">
-        <v>354534.24</v>
+        <v>326421.08</v>
       </c>
       <c r="P39" t="n">
-        <v>2343913.72</v>
+        <v>2172579.94</v>
       </c>
       <c r="Q39" t="n">
-        <v>2342135.48</v>
+        <v>2172350.65</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -3387,13 +3387,13 @@
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>2342135.48</v>
+        <v>2172350.65</v>
       </c>
       <c r="V39" t="n">
-        <v>2342135.48</v>
+        <v>2172350.65</v>
       </c>
       <c r="W39" t="n">
-        <v>2342135.48</v>
+        <v>2172350.65</v>
       </c>
     </row>
     <row r="40">
@@ -3414,61 +3414,61 @@
         <v>0.0364</v>
       </c>
       <c r="E40" t="n">
-        <v>4.488444548261857</v>
+        <v>4.601938104014417</v>
       </c>
       <c r="F40" t="n">
-        <v>-2886638.29</v>
+        <v>-2860017.83</v>
       </c>
       <c r="G40" t="n">
-        <v>4343936.12</v>
+        <v>4258916.51</v>
       </c>
       <c r="H40" t="n">
-        <v>1457297.84</v>
+        <v>1398898.69</v>
       </c>
       <c r="I40" t="n">
-        <v>45977.58</v>
+        <v>45125.31</v>
       </c>
       <c r="J40" t="n">
-        <v>245692.2168598445</v>
+        <v>228098.8668659362</v>
       </c>
       <c r="K40" t="n">
-        <v>245692.22</v>
+        <v>228098.87</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>147212.74</v>
+        <v>139646.67</v>
       </c>
       <c r="N40" t="n">
-        <v>147212.74</v>
+        <v>139646.67</v>
       </c>
       <c r="O40" t="n">
-        <v>438882.53</v>
+        <v>412870.85</v>
       </c>
       <c r="P40" t="n">
-        <v>1018331.98</v>
+        <v>986010.24</v>
       </c>
       <c r="Q40" t="n">
-        <v>1018415.3</v>
+        <v>986027.84</v>
       </c>
       <c r="R40" t="n">
-        <v>62987.77</v>
+        <v>117673.92</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>62987.77</v>
+        <v>117673.92</v>
       </c>
       <c r="U40" t="n">
-        <v>955427.53</v>
+        <v>868353.92</v>
       </c>
       <c r="V40" t="n">
-        <v>1018415.3</v>
+        <v>986027.84</v>
       </c>
       <c r="W40" t="n">
-        <v>955427.53</v>
+        <v>868353.92</v>
       </c>
     </row>
     <row r="41">
@@ -3489,43 +3489,43 @@
         <v>0.0363</v>
       </c>
       <c r="E41" t="n">
-        <v>4.651764424776601</v>
+        <v>4.754286995688718</v>
       </c>
       <c r="F41" t="n">
-        <v>13258894.86</v>
+        <v>11761649.26</v>
       </c>
       <c r="G41" t="n">
-        <v>-13534181.04</v>
+        <v>-12072502.01</v>
       </c>
       <c r="H41" t="n">
-        <v>-275286.18</v>
+        <v>-310852.76</v>
       </c>
       <c r="I41" t="n">
-        <v>49130.02</v>
+        <v>46120.04</v>
       </c>
       <c r="J41" t="n">
-        <v>119177.8819166915</v>
+        <v>110732.3973792512</v>
       </c>
       <c r="K41" t="n">
-        <v>119177.88</v>
+        <v>110732.4</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>73514.16</v>
+        <v>69355.5</v>
       </c>
       <c r="N41" t="n">
-        <v>73514.16</v>
+        <v>69355.5</v>
       </c>
       <c r="O41" t="n">
-        <v>241822.07</v>
+        <v>226207.93</v>
       </c>
       <c r="P41" t="n">
-        <v>-517108.25</v>
+        <v>-537060.6899999999</v>
       </c>
       <c r="Q41" t="n">
-        <v>-517108.25</v>
+        <v>-537060.6899999999</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -3537,13 +3537,13 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>-517108.25</v>
+        <v>-537060.6899999999</v>
       </c>
       <c r="V41" t="n">
-        <v>-517108.25</v>
+        <v>-537060.6899999999</v>
       </c>
       <c r="W41" t="n">
-        <v>-517108.25</v>
+        <v>-537060.6899999999</v>
       </c>
     </row>
   </sheetData>
@@ -3629,37 +3629,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>28944022.05</v>
+        <v>25023405.33</v>
       </c>
       <c r="C2" t="n">
-        <v>1083607.9</v>
+        <v>1015531.17</v>
       </c>
       <c r="D2" t="n">
-        <v>2744572.82</v>
+        <v>2516092.17</v>
       </c>
       <c r="E2" t="n">
-        <v>4602961.04</v>
+        <v>4114390.54</v>
       </c>
       <c r="F2" t="n">
-        <v>8431141.76</v>
+        <v>7646013.87</v>
       </c>
       <c r="G2" t="n">
-        <v>20815731.02</v>
+        <v>17675141.23</v>
       </c>
       <c r="H2" t="n">
-        <v>20512880.3</v>
+        <v>17377391.46</v>
       </c>
       <c r="I2" t="n">
-        <v>282712.55</v>
+        <v>1146719.66</v>
       </c>
       <c r="J2" t="n">
-        <v>489501.81</v>
+        <v>2320918.9</v>
       </c>
       <c r="K2" t="n">
-        <v>772214.36</v>
+        <v>3467638.56</v>
       </c>
       <c r="L2" t="n">
-        <v>19740665.94</v>
+        <v>13909752.9</v>
       </c>
     </row>
   </sheetData>

--- a/notebooks/data/backtest/monthly_attribution_v11.xlsx
+++ b/notebooks/data/backtest/monthly_attribution_v11.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W41"/>
+  <dimension ref="A1:W40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -564,43 +564,43 @@
         <v>0.0432</v>
       </c>
       <c r="E2" t="n">
-        <v>4.257089152151979</v>
+        <v>4.263817071707896</v>
       </c>
       <c r="F2" t="n">
-        <v>6179553.59</v>
+        <v>6239432.78</v>
       </c>
       <c r="G2" t="n">
-        <v>-4934019.63</v>
+        <v>-4960312.24</v>
       </c>
       <c r="H2" t="n">
-        <v>1245533.96</v>
+        <v>1279120.54</v>
       </c>
       <c r="I2" t="n">
-        <v>14520.82</v>
+        <v>13966.05</v>
       </c>
       <c r="J2" t="n">
-        <v>12251.11388244837</v>
+        <v>11746.93641559852</v>
       </c>
       <c r="K2" t="n">
-        <v>12251.11</v>
+        <v>11746.94</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>54142.82</v>
+        <v>54030.15</v>
       </c>
       <c r="N2" t="n">
-        <v>54142.82</v>
+        <v>54030.15</v>
       </c>
       <c r="O2" t="n">
-        <v>80914.75</v>
+        <v>79743.13</v>
       </c>
       <c r="P2" t="n">
-        <v>1450218.81</v>
+        <v>1462351.74</v>
       </c>
       <c r="Q2" t="n">
-        <v>1164619.21</v>
+        <v>1199377.4</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -612,13 +612,13 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1164619.21</v>
+        <v>1199377.4</v>
       </c>
       <c r="V2" t="n">
-        <v>1164619.21</v>
+        <v>1199377.4</v>
       </c>
       <c r="W2" t="n">
-        <v>1164619.21</v>
+        <v>1199377.4</v>
       </c>
     </row>
     <row r="3">
@@ -639,43 +639,43 @@
         <v>0.0457</v>
       </c>
       <c r="E3" t="n">
-        <v>4.149520760987008</v>
+        <v>4.155851254717449</v>
       </c>
       <c r="F3" t="n">
-        <v>1150488.38</v>
+        <v>825595.47</v>
       </c>
       <c r="G3" t="n">
-        <v>-510557.69</v>
+        <v>-281419.42</v>
       </c>
       <c r="H3" t="n">
-        <v>639930.6800000001</v>
+        <v>544176.05</v>
       </c>
       <c r="I3" t="n">
-        <v>3112.5</v>
+        <v>2966.99</v>
       </c>
       <c r="J3" t="n">
-        <v>12568.71122234015</v>
+        <v>12023.67524185553</v>
       </c>
       <c r="K3" t="n">
-        <v>12568.71</v>
+        <v>12023.68</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>59667.54</v>
+        <v>59358.81</v>
       </c>
       <c r="N3" t="n">
-        <v>59667.54</v>
+        <v>59358.81</v>
       </c>
       <c r="O3" t="n">
-        <v>75348.75</v>
+        <v>74349.47</v>
       </c>
       <c r="P3" t="n">
-        <v>564581.9300000001</v>
+        <v>469826.58</v>
       </c>
       <c r="Q3" t="n">
-        <v>564581.9300000001</v>
+        <v>469826.58</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -687,13 +687,13 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>564581.9300000001</v>
+        <v>469826.58</v>
       </c>
       <c r="V3" t="n">
-        <v>564581.9300000001</v>
+        <v>469826.58</v>
       </c>
       <c r="W3" t="n">
-        <v>564581.9300000001</v>
+        <v>469826.58</v>
       </c>
     </row>
     <row r="4">
@@ -714,61 +714,61 @@
         <v>0.0482</v>
       </c>
       <c r="E4" t="n">
-        <v>4.207384876860384</v>
+        <v>4.212916610837371</v>
       </c>
       <c r="F4" t="n">
-        <v>4323329.45</v>
+        <v>4195768.01</v>
       </c>
       <c r="G4" t="n">
-        <v>-3493421.39</v>
+        <v>-3373702.78</v>
       </c>
       <c r="H4" t="n">
-        <v>829908.0600000001</v>
+        <v>822065.24</v>
       </c>
       <c r="I4" t="n">
-        <v>16009.24</v>
+        <v>15550.29</v>
       </c>
       <c r="J4" t="n">
-        <v>15672.09570156108</v>
+        <v>14924.5907609542</v>
       </c>
       <c r="K4" t="n">
-        <v>15672.1</v>
+        <v>14924.59</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>76895.71000000001</v>
+        <v>76163.46000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>76895.71000000001</v>
+        <v>76163.46000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>108577.04</v>
+        <v>106638.35</v>
       </c>
       <c r="P4" t="n">
-        <v>721331.02</v>
+        <v>715426.89</v>
       </c>
       <c r="Q4" t="n">
-        <v>721331.02</v>
+        <v>715426.89</v>
       </c>
       <c r="R4" t="n">
-        <v>49738.26</v>
+        <v>49739.57</v>
       </c>
       <c r="S4" t="n">
-        <v>437690.12</v>
+        <v>457676.03</v>
       </c>
       <c r="T4" t="n">
-        <v>487428.37</v>
+        <v>507415.61</v>
       </c>
       <c r="U4" t="n">
-        <v>233902.65</v>
+        <v>208011.28</v>
       </c>
       <c r="V4" t="n">
-        <v>721331.02</v>
+        <v>715426.89</v>
       </c>
       <c r="W4" t="n">
-        <v>233902.65</v>
+        <v>208011.28</v>
       </c>
     </row>
     <row r="5">
@@ -789,43 +789,43 @@
         <v>0.0481</v>
       </c>
       <c r="E5" t="n">
-        <v>4.242716035080737</v>
+        <v>4.24933576196015</v>
       </c>
       <c r="F5" t="n">
-        <v>-737545.4</v>
+        <v>-661535.79</v>
       </c>
       <c r="G5" t="n">
-        <v>816416.16</v>
+        <v>743562.34</v>
       </c>
       <c r="H5" t="n">
-        <v>78870.75999999999</v>
+        <v>82026.55</v>
       </c>
       <c r="I5" t="n">
-        <v>1984.76</v>
+        <v>1915.78</v>
       </c>
       <c r="J5" t="n">
-        <v>12538.66899760892</v>
+        <v>11889.883340327</v>
       </c>
       <c r="K5" t="n">
-        <v>12538.67</v>
+        <v>11889.88</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>68607.23</v>
+        <v>68004.21000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>68607.23</v>
+        <v>68004.21000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>83130.67</v>
+        <v>81809.87</v>
       </c>
       <c r="P5" t="n">
-        <v>-4259.91</v>
+        <v>216.68</v>
       </c>
       <c r="Q5" t="n">
-        <v>-4259.91</v>
+        <v>216.68</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -837,13 +837,13 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-4259.91</v>
+        <v>216.68</v>
       </c>
       <c r="V5" t="n">
-        <v>-4259.91</v>
+        <v>216.68</v>
       </c>
       <c r="W5" t="n">
-        <v>-4259.91</v>
+        <v>216.68</v>
       </c>
     </row>
     <row r="6">
@@ -864,43 +864,43 @@
         <v>0.0507</v>
       </c>
       <c r="E6" t="n">
-        <v>4.243224349689947</v>
+        <v>4.255137956966056</v>
       </c>
       <c r="F6" t="n">
-        <v>3794070.54</v>
+        <v>3870700.27</v>
       </c>
       <c r="G6" t="n">
-        <v>-2700566.54</v>
+        <v>-2760060.67</v>
       </c>
       <c r="H6" t="n">
-        <v>1093504</v>
+        <v>1110639.6</v>
       </c>
       <c r="I6" t="n">
-        <v>2249.35</v>
+        <v>2096.7</v>
       </c>
       <c r="J6" t="n">
-        <v>14208.71652464574</v>
+        <v>13463.42459581242</v>
       </c>
       <c r="K6" t="n">
-        <v>14208.72</v>
+        <v>13463.42</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>85427.38</v>
+        <v>84967.25999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>85427.38</v>
+        <v>84967.25999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>101885.45</v>
+        <v>100527.39</v>
       </c>
       <c r="P6" t="n">
-        <v>991618.55</v>
+        <v>1010112.21</v>
       </c>
       <c r="Q6" t="n">
-        <v>991618.55</v>
+        <v>1010112.21</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -912,13 +912,13 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>991618.55</v>
+        <v>1010112.21</v>
       </c>
       <c r="V6" t="n">
-        <v>991618.55</v>
+        <v>1010112.21</v>
       </c>
       <c r="W6" t="n">
-        <v>991618.55</v>
+        <v>1010112.21</v>
       </c>
     </row>
     <row r="7">
@@ -939,61 +939,61 @@
         <v>0.0507</v>
       </c>
       <c r="E7" t="n">
-        <v>4.21212733025512</v>
+        <v>4.222493566862488</v>
       </c>
       <c r="F7" t="n">
-        <v>3001083.27</v>
+        <v>3011123.32</v>
       </c>
       <c r="G7" t="n">
-        <v>-2223007.27</v>
+        <v>-2225758.1</v>
       </c>
       <c r="H7" t="n">
-        <v>778076.01</v>
+        <v>785365.22</v>
       </c>
       <c r="I7" t="n">
-        <v>13196.99</v>
+        <v>12800.64</v>
       </c>
       <c r="J7" t="n">
-        <v>15942.70043318396</v>
+        <v>15155.51150366273</v>
       </c>
       <c r="K7" t="n">
-        <v>15942.7</v>
+        <v>15155.51</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>87569.8</v>
+        <v>87081.64</v>
       </c>
       <c r="N7" t="n">
-        <v>87569.8</v>
+        <v>87081.64</v>
       </c>
       <c r="O7" t="n">
-        <v>116709.49</v>
+        <v>115037.79</v>
       </c>
       <c r="P7" t="n">
-        <v>661366.52</v>
+        <v>670327.4300000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>661366.52</v>
+        <v>670327.4300000001</v>
       </c>
       <c r="R7" t="n">
-        <v>62536.78</v>
+        <v>63103.49</v>
       </c>
       <c r="S7" t="n">
-        <v>288506.56</v>
+        <v>268706.32</v>
       </c>
       <c r="T7" t="n">
-        <v>351043.35</v>
+        <v>331809.82</v>
       </c>
       <c r="U7" t="n">
-        <v>310323.17</v>
+        <v>338517.61</v>
       </c>
       <c r="V7" t="n">
-        <v>661366.52</v>
+        <v>670327.4300000001</v>
       </c>
       <c r="W7" t="n">
-        <v>310323.17</v>
+        <v>338517.61</v>
       </c>
     </row>
     <row r="8">
@@ -1014,43 +1014,43 @@
         <v>0.0532</v>
       </c>
       <c r="E8" t="n">
-        <v>4.240974625819007</v>
+        <v>4.246950373001004</v>
       </c>
       <c r="F8" t="n">
-        <v>5233575.63</v>
+        <v>4993040.41</v>
       </c>
       <c r="G8" t="n">
-        <v>-4106309.44</v>
+        <v>-3903836.23</v>
       </c>
       <c r="H8" t="n">
-        <v>1127266.2</v>
+        <v>1089204.18</v>
       </c>
       <c r="I8" t="n">
-        <v>11169.83</v>
+        <v>10636.65</v>
       </c>
       <c r="J8" t="n">
-        <v>17785.1125683979</v>
+        <v>16953.92563339959</v>
       </c>
       <c r="K8" t="n">
-        <v>17785.11</v>
+        <v>16953.93</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>90908.25999999999</v>
+        <v>90219.87</v>
       </c>
       <c r="N8" t="n">
-        <v>90908.25999999999</v>
+        <v>90219.87</v>
       </c>
       <c r="O8" t="n">
-        <v>119863.2</v>
+        <v>117810.45</v>
       </c>
       <c r="P8" t="n">
-        <v>1007403</v>
+        <v>971393.73</v>
       </c>
       <c r="Q8" t="n">
-        <v>1007403</v>
+        <v>971393.73</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1062,13 +1062,13 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1007403</v>
+        <v>971393.73</v>
       </c>
       <c r="V8" t="n">
-        <v>1007403</v>
+        <v>971393.73</v>
       </c>
       <c r="W8" t="n">
-        <v>1007403</v>
+        <v>971393.73</v>
       </c>
     </row>
     <row r="9">
@@ -1089,43 +1089,43 @@
         <v>0.0532</v>
       </c>
       <c r="E9" t="n">
-        <v>4.149709044470077</v>
+        <v>4.162128435699474</v>
       </c>
       <c r="F9" t="n">
-        <v>-1994816.05</v>
+        <v>-1764856.51</v>
       </c>
       <c r="G9" t="n">
-        <v>1796040.41</v>
+        <v>1615204.04</v>
       </c>
       <c r="H9" t="n">
-        <v>-198775.64</v>
+        <v>-149652.46</v>
       </c>
       <c r="I9" t="n">
-        <v>8485.309999999999</v>
+        <v>8206.860000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>18336.49232064345</v>
+        <v>17474.93295811387</v>
       </c>
       <c r="K9" t="n">
-        <v>18336.49</v>
+        <v>17474.93</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>102760.41</v>
+        <v>102520.23</v>
       </c>
       <c r="N9" t="n">
-        <v>102760.41</v>
+        <v>102520.23</v>
       </c>
       <c r="O9" t="n">
-        <v>129582.22</v>
+        <v>128202.02</v>
       </c>
       <c r="P9" t="n">
-        <v>-328357.86</v>
+        <v>-277854.48</v>
       </c>
       <c r="Q9" t="n">
-        <v>-328357.86</v>
+        <v>-277854.48</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1137,13 +1137,13 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>-328357.86</v>
+        <v>-277854.48</v>
       </c>
       <c r="V9" t="n">
-        <v>-328357.86</v>
+        <v>-277854.48</v>
       </c>
       <c r="W9" t="n">
-        <v>-328357.86</v>
+        <v>-277854.48</v>
       </c>
     </row>
     <row r="10">
@@ -1164,61 +1164,61 @@
         <v>0.0532</v>
       </c>
       <c r="E10" t="n">
-        <v>4.374095437666899</v>
+        <v>4.372154019949081</v>
       </c>
       <c r="F10" t="n">
-        <v>-2488841.93</v>
+        <v>-2561888.75</v>
       </c>
       <c r="G10" t="n">
-        <v>2276618.65</v>
+        <v>2314580.88</v>
       </c>
       <c r="H10" t="n">
-        <v>-212223.28</v>
+        <v>-247307.87</v>
       </c>
       <c r="I10" t="n">
-        <v>13015.89</v>
+        <v>11948.35</v>
       </c>
       <c r="J10" t="n">
-        <v>16904.64097853862</v>
+        <v>16154.22368128838</v>
       </c>
       <c r="K10" t="n">
-        <v>16904.64</v>
+        <v>16154.22</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>97664.08</v>
+        <v>96931.41</v>
       </c>
       <c r="N10" t="n">
-        <v>97664.08</v>
+        <v>96931.41</v>
       </c>
       <c r="O10" t="n">
-        <v>127584.61</v>
+        <v>125033.98</v>
       </c>
       <c r="P10" t="n">
-        <v>-336673.53</v>
+        <v>-369434.56</v>
       </c>
       <c r="Q10" t="n">
-        <v>-339807.89</v>
+        <v>-372341.85</v>
       </c>
       <c r="R10" t="n">
-        <v>70973.02</v>
+        <v>70949.59</v>
       </c>
       <c r="S10" t="n">
-        <v>46609.72</v>
+        <v>45603.67</v>
       </c>
       <c r="T10" t="n">
-        <v>117582.74</v>
+        <v>116553.26</v>
       </c>
       <c r="U10" t="n">
-        <v>-457390.63</v>
+        <v>-488895.11</v>
       </c>
       <c r="V10" t="n">
-        <v>-339807.89</v>
+        <v>-372341.85</v>
       </c>
       <c r="W10" t="n">
-        <v>-457390.63</v>
+        <v>-488895.11</v>
       </c>
     </row>
     <row r="11">
@@ -1239,43 +1239,43 @@
         <v>0.0532</v>
       </c>
       <c r="E11" t="n">
-        <v>4.307605054817456</v>
+        <v>4.308572157623782</v>
       </c>
       <c r="F11" t="n">
-        <v>-1284572.35</v>
+        <v>-1009172.37</v>
       </c>
       <c r="G11" t="n">
-        <v>1319948.46</v>
+        <v>1105069.36</v>
       </c>
       <c r="H11" t="n">
-        <v>35376.11</v>
+        <v>95896.99000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>6140.52</v>
+        <v>5710.15</v>
       </c>
       <c r="J11" t="n">
-        <v>17672.5876409492</v>
+        <v>16915.25112923859</v>
       </c>
       <c r="K11" t="n">
-        <v>17672.59</v>
+        <v>16915.25</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>102989.19</v>
+        <v>102211.65</v>
       </c>
       <c r="N11" t="n">
-        <v>102989.19</v>
+        <v>102211.65</v>
       </c>
       <c r="O11" t="n">
-        <v>126802.29</v>
+        <v>124837.05</v>
       </c>
       <c r="P11" t="n">
-        <v>-90471.27</v>
+        <v>-28082.74</v>
       </c>
       <c r="Q11" t="n">
-        <v>-91426.17999999999</v>
+        <v>-28940.06</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1287,13 +1287,13 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>-91426.17999999999</v>
+        <v>-28940.06</v>
       </c>
       <c r="V11" t="n">
-        <v>-91426.17999999999</v>
+        <v>-28940.06</v>
       </c>
       <c r="W11" t="n">
-        <v>-91426.17999999999</v>
+        <v>-28940.06</v>
       </c>
     </row>
     <row r="12">
@@ -1314,43 +1314,43 @@
         <v>0.0532</v>
       </c>
       <c r="E12" t="n">
-        <v>4.240405863039348</v>
+        <v>4.248838634513568</v>
       </c>
       <c r="F12" t="n">
-        <v>6851108.91</v>
+        <v>6787121.1</v>
       </c>
       <c r="G12" t="n">
-        <v>-5461859.19</v>
+        <v>-5389444.12</v>
       </c>
       <c r="H12" t="n">
-        <v>1389249.72</v>
+        <v>1397676.99</v>
       </c>
       <c r="I12" t="n">
-        <v>17613.08</v>
+        <v>16948.01</v>
       </c>
       <c r="J12" t="n">
-        <v>23491.41682691433</v>
+        <v>22583.06205155689</v>
       </c>
       <c r="K12" t="n">
-        <v>23491.42</v>
+        <v>22583.06</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>102049.48</v>
+        <v>101893.83</v>
       </c>
       <c r="N12" t="n">
-        <v>102049.48</v>
+        <v>101893.83</v>
       </c>
       <c r="O12" t="n">
-        <v>143153.98</v>
+        <v>141424.9</v>
       </c>
       <c r="P12" t="n">
-        <v>1246095.74</v>
+        <v>1256252.08</v>
       </c>
       <c r="Q12" t="n">
-        <v>1246095.74</v>
+        <v>1256252.08</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1362,13 +1362,13 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1246095.74</v>
+        <v>1256252.08</v>
       </c>
       <c r="V12" t="n">
-        <v>1246095.74</v>
+        <v>1256252.08</v>
       </c>
       <c r="W12" t="n">
-        <v>1246095.74</v>
+        <v>1256252.08</v>
       </c>
     </row>
     <row r="13">
@@ -1389,61 +1389,61 @@
         <v>0.0532</v>
       </c>
       <c r="E13" t="n">
-        <v>4.23593447545381</v>
+        <v>4.245954452109957</v>
       </c>
       <c r="F13" t="n">
-        <v>4231190.08</v>
+        <v>4207036.9</v>
       </c>
       <c r="G13" t="n">
-        <v>-3170000.87</v>
+        <v>-3147426.87</v>
       </c>
       <c r="H13" t="n">
-        <v>1061189.21</v>
+        <v>1059610.04</v>
       </c>
       <c r="I13" t="n">
-        <v>12778.73</v>
+        <v>12387.47</v>
       </c>
       <c r="J13" t="n">
-        <v>25732.77410576204</v>
+        <v>24837.92997677973</v>
       </c>
       <c r="K13" t="n">
-        <v>25732.77</v>
+        <v>24837.93</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>102370.49</v>
+        <v>102396.55</v>
       </c>
       <c r="N13" t="n">
-        <v>102370.49</v>
+        <v>102396.55</v>
       </c>
       <c r="O13" t="n">
-        <v>140881.99</v>
+        <v>139621.94</v>
       </c>
       <c r="P13" t="n">
-        <v>920307.22</v>
+        <v>919988.09</v>
       </c>
       <c r="Q13" t="n">
-        <v>920307.22</v>
+        <v>919988.09</v>
       </c>
       <c r="R13" t="n">
-        <v>72335.94</v>
+        <v>72281.19</v>
       </c>
       <c r="S13" t="n">
-        <v>329881.22</v>
+        <v>336049.44</v>
       </c>
       <c r="T13" t="n">
-        <v>402217.17</v>
+        <v>408330.63</v>
       </c>
       <c r="U13" t="n">
-        <v>518090.06</v>
+        <v>511657.46</v>
       </c>
       <c r="V13" t="n">
-        <v>920307.22</v>
+        <v>919988.09</v>
       </c>
       <c r="W13" t="n">
-        <v>518090.06</v>
+        <v>511657.46</v>
       </c>
     </row>
     <row r="14">
@@ -1464,43 +1464,43 @@
         <v>0.0532</v>
       </c>
       <c r="E14" t="n">
-        <v>4.160898435358346</v>
+        <v>4.166147223794693</v>
       </c>
       <c r="F14" t="n">
-        <v>-755988.77</v>
+        <v>-778841.37</v>
       </c>
       <c r="G14" t="n">
-        <v>1023209.84</v>
+        <v>1026242.14</v>
       </c>
       <c r="H14" t="n">
-        <v>267221.07</v>
+        <v>247400.77</v>
       </c>
       <c r="I14" t="n">
-        <v>12390.22</v>
+        <v>11619.52</v>
       </c>
       <c r="J14" t="n">
-        <v>22745.29360984699</v>
+        <v>21854.80372730174</v>
       </c>
       <c r="K14" t="n">
-        <v>22745.29</v>
+        <v>21854.8</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>105932.1</v>
+        <v>105718.58</v>
       </c>
       <c r="N14" t="n">
-        <v>105932.1</v>
+        <v>105718.58</v>
       </c>
       <c r="O14" t="n">
-        <v>141067.61</v>
+        <v>139192.9</v>
       </c>
       <c r="P14" t="n">
-        <v>123130.63</v>
+        <v>105421.66</v>
       </c>
       <c r="Q14" t="n">
-        <v>126153.46</v>
+        <v>108207.87</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1512,13 +1512,13 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>126153.46</v>
+        <v>108207.87</v>
       </c>
       <c r="V14" t="n">
-        <v>126153.46</v>
+        <v>108207.87</v>
       </c>
       <c r="W14" t="n">
-        <v>126153.46</v>
+        <v>108207.87</v>
       </c>
     </row>
     <row r="15">
@@ -1539,43 +1539,43 @@
         <v>0.0532</v>
       </c>
       <c r="E15" t="n">
-        <v>4.23726598863084</v>
+        <v>4.241443270794358</v>
       </c>
       <c r="F15" t="n">
-        <v>8461101.619999999</v>
+        <v>8471380.609999999</v>
       </c>
       <c r="G15" t="n">
-        <v>-7961945.45</v>
+        <v>-7891776.11</v>
       </c>
       <c r="H15" t="n">
-        <v>499156.17</v>
+        <v>579604.5</v>
       </c>
       <c r="I15" t="n">
-        <v>27167.87</v>
+        <v>26719.94</v>
       </c>
       <c r="J15" t="n">
-        <v>23439.75368639317</v>
+        <v>22746.58477148094</v>
       </c>
       <c r="K15" t="n">
-        <v>23439.75</v>
+        <v>22746.58</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>106719.48</v>
+        <v>106855.38</v>
       </c>
       <c r="N15" t="n">
-        <v>106719.48</v>
+        <v>106855.38</v>
       </c>
       <c r="O15" t="n">
-        <v>157327.1</v>
+        <v>156321.9</v>
       </c>
       <c r="P15" t="n">
-        <v>341829.07</v>
+        <v>423282.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>341829.07</v>
+        <v>423282.6</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -1587,13 +1587,13 @@
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>341829.07</v>
+        <v>423282.6</v>
       </c>
       <c r="V15" t="n">
-        <v>341829.07</v>
+        <v>423282.6</v>
       </c>
       <c r="W15" t="n">
-        <v>341829.07</v>
+        <v>423282.6</v>
       </c>
     </row>
     <row r="16">
@@ -1614,61 +1614,61 @@
         <v>0.0533</v>
       </c>
       <c r="E16" t="n">
-        <v>4.319441526751256</v>
+        <v>4.328693541538845</v>
       </c>
       <c r="F16" t="n">
-        <v>3981850.78</v>
+        <v>3879212.55</v>
       </c>
       <c r="G16" t="n">
-        <v>-3549420.01</v>
+        <v>-3446886.54</v>
       </c>
       <c r="H16" t="n">
-        <v>432430.77</v>
+        <v>432326.02</v>
       </c>
       <c r="I16" t="n">
-        <v>15853.93</v>
+        <v>16489.03</v>
       </c>
       <c r="J16" t="n">
-        <v>24684.15119403339</v>
+        <v>24016.02893995139</v>
       </c>
       <c r="K16" t="n">
-        <v>24684.15</v>
+        <v>24016.03</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>110197.18</v>
+        <v>110532.59</v>
       </c>
       <c r="N16" t="n">
-        <v>110197.18</v>
+        <v>110532.59</v>
       </c>
       <c r="O16" t="n">
-        <v>150735.26</v>
+        <v>151037.65</v>
       </c>
       <c r="P16" t="n">
-        <v>281980.53</v>
+        <v>281865.02</v>
       </c>
       <c r="Q16" t="n">
-        <v>281695.51</v>
+        <v>281288.36</v>
       </c>
       <c r="R16" t="n">
-        <v>81982.02</v>
+        <v>82093.67</v>
       </c>
       <c r="S16" t="n">
-        <v>155967.26</v>
+        <v>114778.69</v>
       </c>
       <c r="T16" t="n">
-        <v>237949.28</v>
+        <v>196872.36</v>
       </c>
       <c r="U16" t="n">
-        <v>43746.23</v>
+        <v>84416.00999999999</v>
       </c>
       <c r="V16" t="n">
-        <v>281695.51</v>
+        <v>281288.36</v>
       </c>
       <c r="W16" t="n">
-        <v>43746.23</v>
+        <v>84416.00999999999</v>
       </c>
     </row>
     <row r="17">
@@ -1689,43 +1689,43 @@
         <v>0.0532</v>
       </c>
       <c r="E17" t="n">
-        <v>4.28305584662614</v>
+        <v>4.355240195547058</v>
       </c>
       <c r="F17" t="n">
-        <v>-2332769.16</v>
+        <v>-2513149.18</v>
       </c>
       <c r="G17" t="n">
-        <v>2462026.24</v>
+        <v>2752220.51</v>
       </c>
       <c r="H17" t="n">
-        <v>129257.08</v>
+        <v>239071.33</v>
       </c>
       <c r="I17" t="n">
-        <v>24799.61</v>
+        <v>20766.23</v>
       </c>
       <c r="J17" t="n">
-        <v>26324.84780952142</v>
+        <v>25595.72479730571</v>
       </c>
       <c r="K17" t="n">
-        <v>26324.85</v>
+        <v>25595.72</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>121872.63</v>
+        <v>124725.43</v>
       </c>
       <c r="N17" t="n">
-        <v>121872.63</v>
+        <v>124725.43</v>
       </c>
       <c r="O17" t="n">
-        <v>172997.08</v>
+        <v>171087.38</v>
       </c>
       <c r="P17" t="n">
-        <v>-43790.26</v>
+        <v>67938.53</v>
       </c>
       <c r="Q17" t="n">
-        <v>-43740</v>
+        <v>67983.95</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -1737,13 +1737,13 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>-43740</v>
+        <v>67983.95</v>
       </c>
       <c r="V17" t="n">
-        <v>-43740</v>
+        <v>67983.95</v>
       </c>
       <c r="W17" t="n">
-        <v>-43740</v>
+        <v>67983.95</v>
       </c>
     </row>
     <row r="18">
@@ -1764,43 +1764,43 @@
         <v>0.0532</v>
       </c>
       <c r="E18" t="n">
-        <v>4.23501016408488</v>
+        <v>4.251968729649042</v>
       </c>
       <c r="F18" t="n">
-        <v>4854990.41</v>
+        <v>4538980.98</v>
       </c>
       <c r="G18" t="n">
-        <v>-4483908.27</v>
+        <v>-4141113.5</v>
       </c>
       <c r="H18" t="n">
-        <v>371082.14</v>
+        <v>397867.47</v>
       </c>
       <c r="I18" t="n">
-        <v>13455.48</v>
+        <v>12979.4</v>
       </c>
       <c r="J18" t="n">
-        <v>25111.94152888906</v>
+        <v>24109.23326309334</v>
       </c>
       <c r="K18" t="n">
-        <v>25111.94</v>
+        <v>24109.23</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>120705.52</v>
+        <v>122236.24</v>
       </c>
       <c r="N18" t="n">
-        <v>120705.52</v>
+        <v>122236.24</v>
       </c>
       <c r="O18" t="n">
-        <v>159272.94</v>
+        <v>159324.87</v>
       </c>
       <c r="P18" t="n">
-        <v>211809.2</v>
+        <v>238542.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>211809.2</v>
+        <v>238542.6</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -1812,13 +1812,13 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>211809.2</v>
+        <v>238542.6</v>
       </c>
       <c r="V18" t="n">
-        <v>211809.2</v>
+        <v>238542.6</v>
       </c>
       <c r="W18" t="n">
-        <v>211809.2</v>
+        <v>238542.6</v>
       </c>
     </row>
     <row r="19">
@@ -1839,61 +1839,61 @@
         <v>0.0532</v>
       </c>
       <c r="E19" t="n">
-        <v>4.306400725633772</v>
+        <v>4.318329548529479</v>
       </c>
       <c r="F19" t="n">
-        <v>2014039.84</v>
+        <v>2125924.18</v>
       </c>
       <c r="G19" t="n">
-        <v>-1707414.05</v>
+        <v>-1818801.98</v>
       </c>
       <c r="H19" t="n">
-        <v>306625.78</v>
+        <v>307122.2</v>
       </c>
       <c r="I19" t="n">
-        <v>9126.6</v>
+        <v>8764.25</v>
       </c>
       <c r="J19" t="n">
-        <v>22408.21992674831</v>
+        <v>21516.92184315372</v>
       </c>
       <c r="K19" t="n">
-        <v>22408.22</v>
+        <v>21516.92</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>106615.53</v>
+        <v>107882.23</v>
       </c>
       <c r="N19" t="n">
-        <v>106615.53</v>
+        <v>107882.23</v>
       </c>
       <c r="O19" t="n">
-        <v>138150.35</v>
+        <v>138163.41</v>
       </c>
       <c r="P19" t="n">
-        <v>168672.92</v>
+        <v>169135.41</v>
       </c>
       <c r="Q19" t="n">
-        <v>168475.43</v>
+        <v>168958.79</v>
       </c>
       <c r="R19" t="n">
-        <v>86422.88</v>
+        <v>85325.56</v>
       </c>
       <c r="S19" t="n">
-        <v>90276.47</v>
+        <v>42865.82</v>
       </c>
       <c r="T19" t="n">
-        <v>176699.35</v>
+        <v>128191.38</v>
       </c>
       <c r="U19" t="n">
-        <v>-8223.92</v>
+        <v>40767.41</v>
       </c>
       <c r="V19" t="n">
-        <v>168475.43</v>
+        <v>168958.79</v>
       </c>
       <c r="W19" t="n">
-        <v>-8223.92</v>
+        <v>40767.41</v>
       </c>
     </row>
     <row r="20">
@@ -1914,43 +1914,43 @@
         <v>0.0532</v>
       </c>
       <c r="E20" t="n">
-        <v>4.232871245974343</v>
+        <v>4.244295262226552</v>
       </c>
       <c r="F20" t="n">
-        <v>953759.3100000001</v>
+        <v>717676.0600000001</v>
       </c>
       <c r="G20" t="n">
-        <v>-627575.33</v>
+        <v>-404424.02</v>
       </c>
       <c r="H20" t="n">
-        <v>326183.98</v>
+        <v>313252.04</v>
       </c>
       <c r="I20" t="n">
-        <v>26039.84</v>
+        <v>26172.18</v>
       </c>
       <c r="J20" t="n">
-        <v>26254.90954906872</v>
+        <v>25266.79862552829</v>
       </c>
       <c r="K20" t="n">
-        <v>26254.91</v>
+        <v>25266.8</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>120448.81</v>
+        <v>121867.49</v>
       </c>
       <c r="N20" t="n">
-        <v>120448.81</v>
+        <v>121867.49</v>
       </c>
       <c r="O20" t="n">
-        <v>172743.56</v>
+        <v>173306.47</v>
       </c>
       <c r="P20" t="n">
-        <v>154073.69</v>
+        <v>140524.01</v>
       </c>
       <c r="Q20" t="n">
-        <v>153440.41</v>
+        <v>139945.57</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -1962,13 +1962,13 @@
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>153440.41</v>
+        <v>139945.57</v>
       </c>
       <c r="V20" t="n">
-        <v>153440.41</v>
+        <v>139945.57</v>
       </c>
       <c r="W20" t="n">
-        <v>153440.41</v>
+        <v>139945.57</v>
       </c>
     </row>
     <row r="21">
@@ -1989,43 +1989,43 @@
         <v>0.0532</v>
       </c>
       <c r="E21" t="n">
-        <v>4.175523178337027</v>
+        <v>4.192071409466506</v>
       </c>
       <c r="F21" t="n">
-        <v>-1410585.42</v>
+        <v>-1489452.48</v>
       </c>
       <c r="G21" t="n">
-        <v>1933093.57</v>
+        <v>2013654.31</v>
       </c>
       <c r="H21" t="n">
-        <v>522508.15</v>
+        <v>524201.84</v>
       </c>
       <c r="I21" t="n">
-        <v>28532.65</v>
+        <v>28220.7</v>
       </c>
       <c r="J21" t="n">
-        <v>24741.98697499681</v>
+        <v>23873.19719559205</v>
       </c>
       <c r="K21" t="n">
-        <v>24741.99</v>
+        <v>23873.2</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>121029</v>
+        <v>122588.11</v>
       </c>
       <c r="N21" t="n">
-        <v>121029</v>
+        <v>122588.11</v>
       </c>
       <c r="O21" t="n">
-        <v>174303.64</v>
+        <v>174682.01</v>
       </c>
       <c r="P21" t="n">
-        <v>348204.51</v>
+        <v>349519.83</v>
       </c>
       <c r="Q21" t="n">
-        <v>348204.51</v>
+        <v>349519.83</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2037,13 +2037,13 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>348204.51</v>
+        <v>349519.83</v>
       </c>
       <c r="V21" t="n">
-        <v>348204.51</v>
+        <v>349519.83</v>
       </c>
       <c r="W21" t="n">
-        <v>348204.51</v>
+        <v>349519.83</v>
       </c>
     </row>
     <row r="22">
@@ -2064,61 +2064,61 @@
         <v>0.0483</v>
       </c>
       <c r="E22" t="n">
-        <v>4.300151056408744</v>
+        <v>4.318647525430419</v>
       </c>
       <c r="F22" t="n">
-        <v>3515015.79</v>
+        <v>3517693.22</v>
       </c>
       <c r="G22" t="n">
-        <v>-3756284.77</v>
+        <v>-3743345.15</v>
       </c>
       <c r="H22" t="n">
-        <v>-241268.99</v>
+        <v>-225651.92</v>
       </c>
       <c r="I22" t="n">
-        <v>42357.16</v>
+        <v>41747.92</v>
       </c>
       <c r="J22" t="n">
-        <v>26750.84479658073</v>
+        <v>25831.80890210421</v>
       </c>
       <c r="K22" t="n">
-        <v>26750.84</v>
+        <v>25831.81</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>110509.28</v>
+        <v>111940.59</v>
       </c>
       <c r="N22" t="n">
-        <v>110509.28</v>
+        <v>111940.59</v>
       </c>
       <c r="O22" t="n">
-        <v>179617.29</v>
+        <v>179520.32</v>
       </c>
       <c r="P22" t="n">
-        <v>-420499.42</v>
+        <v>-404691.17</v>
       </c>
       <c r="Q22" t="n">
-        <v>-420886.27</v>
+        <v>-405172.24</v>
       </c>
       <c r="R22" t="n">
-        <v>88993.32000000001</v>
+        <v>86532.56</v>
       </c>
       <c r="S22" t="n">
-        <v>8072.55</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>97065.87</v>
+        <v>86532.56</v>
       </c>
       <c r="U22" t="n">
-        <v>-517952.14</v>
+        <v>-491704.8</v>
       </c>
       <c r="V22" t="n">
-        <v>-420886.27</v>
+        <v>-405172.24</v>
       </c>
       <c r="W22" t="n">
-        <v>-517952.14</v>
+        <v>-491704.8</v>
       </c>
     </row>
     <row r="23">
@@ -2139,43 +2139,43 @@
         <v>0.0483</v>
       </c>
       <c r="E23" t="n">
-        <v>4.068699598767902</v>
+        <v>4.093214963987339</v>
       </c>
       <c r="F23" t="n">
-        <v>180688.68</v>
+        <v>-3265.86</v>
       </c>
       <c r="G23" t="n">
-        <v>294507.04</v>
+        <v>488521.17</v>
       </c>
       <c r="H23" t="n">
-        <v>475195.72</v>
+        <v>485255.3</v>
       </c>
       <c r="I23" t="n">
-        <v>24644.97</v>
+        <v>24017.73</v>
       </c>
       <c r="J23" t="n">
-        <v>56705.4632854517</v>
+        <v>54828.595589114</v>
       </c>
       <c r="K23" t="n">
-        <v>56705.46</v>
+        <v>54828.6</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>105981.82</v>
+        <v>107374.31</v>
       </c>
       <c r="N23" t="n">
-        <v>105981.82</v>
+        <v>107374.31</v>
       </c>
       <c r="O23" t="n">
-        <v>187332.26</v>
+        <v>186220.63</v>
       </c>
       <c r="P23" t="n">
-        <v>288320.98</v>
+        <v>299468.29</v>
       </c>
       <c r="Q23" t="n">
-        <v>287863.47</v>
+        <v>299034.67</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -2187,13 +2187,13 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>287863.47</v>
+        <v>299034.67</v>
       </c>
       <c r="V23" t="n">
-        <v>287863.47</v>
+        <v>299034.67</v>
       </c>
       <c r="W23" t="n">
-        <v>287863.47</v>
+        <v>299034.67</v>
       </c>
     </row>
     <row r="24">
@@ -2214,43 +2214,43 @@
         <v>0.0458</v>
       </c>
       <c r="E24" t="n">
-        <v>4.037809810790291</v>
+        <v>4.071938388909778</v>
       </c>
       <c r="F24" t="n">
-        <v>4893396.11</v>
+        <v>4871660.91</v>
       </c>
       <c r="G24" t="n">
-        <v>-4544238.14</v>
+        <v>-4524537.16</v>
       </c>
       <c r="H24" t="n">
-        <v>349157.96</v>
+        <v>347123.75</v>
       </c>
       <c r="I24" t="n">
-        <v>32714.8</v>
+        <v>32767.73</v>
       </c>
       <c r="J24" t="n">
-        <v>53596.15558076301</v>
+        <v>51826.53138176707</v>
       </c>
       <c r="K24" t="n">
-        <v>53596.16</v>
+        <v>51826.53</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>88162.3</v>
+        <v>89569.06</v>
       </c>
       <c r="N24" t="n">
-        <v>88162.3</v>
+        <v>89569.06</v>
       </c>
       <c r="O24" t="n">
-        <v>174473.26</v>
+        <v>174163.33</v>
       </c>
       <c r="P24" t="n">
-        <v>175162.46</v>
+        <v>173410.68</v>
       </c>
       <c r="Q24" t="n">
-        <v>174684.71</v>
+        <v>172960.42</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -2262,13 +2262,13 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>174684.71</v>
+        <v>172960.42</v>
       </c>
       <c r="V24" t="n">
-        <v>174684.71</v>
+        <v>172960.42</v>
       </c>
       <c r="W24" t="n">
-        <v>174684.71</v>
+        <v>172960.42</v>
       </c>
     </row>
     <row r="25">
@@ -2289,61 +2289,61 @@
         <v>0.0433</v>
       </c>
       <c r="E25" t="n">
-        <v>3.999301861018169</v>
+        <v>4.030229767465299</v>
       </c>
       <c r="F25" t="n">
-        <v>47334.2</v>
+        <v>136242</v>
       </c>
       <c r="G25" t="n">
-        <v>963214.46</v>
+        <v>848034.46</v>
       </c>
       <c r="H25" t="n">
-        <v>1010548.66</v>
+        <v>984276.45</v>
       </c>
       <c r="I25" t="n">
-        <v>22338.27</v>
+        <v>22482.88</v>
       </c>
       <c r="J25" t="n">
-        <v>57039.72962825617</v>
+        <v>55482.67523172894</v>
       </c>
       <c r="K25" t="n">
-        <v>57039.73</v>
+        <v>55482.68</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>90340.52</v>
+        <v>91716.77</v>
       </c>
       <c r="N25" t="n">
-        <v>90340.52</v>
+        <v>91716.77</v>
       </c>
       <c r="O25" t="n">
-        <v>169718.52</v>
+        <v>169682.32</v>
       </c>
       <c r="P25" t="n">
-        <v>842668.62</v>
+        <v>816354.98</v>
       </c>
       <c r="Q25" t="n">
-        <v>840830.14</v>
+        <v>814594.13</v>
       </c>
       <c r="R25" t="n">
-        <v>89223.17</v>
+        <v>86494.7</v>
       </c>
       <c r="S25" t="n">
-        <v>216604.61</v>
+        <v>207466.25</v>
       </c>
       <c r="T25" t="n">
-        <v>305827.78</v>
+        <v>293960.95</v>
       </c>
       <c r="U25" t="n">
-        <v>535002.37</v>
+        <v>520633.18</v>
       </c>
       <c r="V25" t="n">
-        <v>840830.14</v>
+        <v>814594.13</v>
       </c>
       <c r="W25" t="n">
-        <v>535002.37</v>
+        <v>520633.18</v>
       </c>
     </row>
     <row r="26">
@@ -2364,43 +2364,43 @@
         <v>0.0433</v>
       </c>
       <c r="E26" t="n">
-        <v>4.020764360631094</v>
+        <v>4.054478911803341</v>
       </c>
       <c r="F26" t="n">
-        <v>1716784.79</v>
+        <v>1818629.35</v>
       </c>
       <c r="G26" t="n">
-        <v>-808651.22</v>
+        <v>-928952.66</v>
       </c>
       <c r="H26" t="n">
-        <v>908133.5600000001</v>
+        <v>889676.6899999999</v>
       </c>
       <c r="I26" t="n">
-        <v>27919.69</v>
+        <v>27970.18</v>
       </c>
       <c r="J26" t="n">
-        <v>57866.29971923039</v>
+        <v>56183.99595772149</v>
       </c>
       <c r="K26" t="n">
-        <v>57866.3</v>
+        <v>56184</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>89103.17</v>
+        <v>90350.03999999999</v>
       </c>
       <c r="N26" t="n">
-        <v>89103.17</v>
+        <v>90350.03999999999</v>
       </c>
       <c r="O26" t="n">
-        <v>174889.16</v>
+        <v>174504.22</v>
       </c>
       <c r="P26" t="n">
-        <v>734197.84</v>
+        <v>716091.72</v>
       </c>
       <c r="Q26" t="n">
-        <v>733244.4</v>
+        <v>715172.48</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -2412,13 +2412,13 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>733244.4</v>
+        <v>715172.48</v>
       </c>
       <c r="V26" t="n">
-        <v>733244.4</v>
+        <v>715172.48</v>
       </c>
       <c r="W26" t="n">
-        <v>733244.4</v>
+        <v>715172.48</v>
       </c>
     </row>
     <row r="27">
@@ -2439,43 +2439,43 @@
         <v>0.0433</v>
       </c>
       <c r="E27" t="n">
-        <v>4.067675932349523</v>
+        <v>4.105700128545985</v>
       </c>
       <c r="F27" t="n">
-        <v>-3503954.84</v>
+        <v>-3765609.18</v>
       </c>
       <c r="G27" t="n">
-        <v>3738504.43</v>
+        <v>4001573.43</v>
       </c>
       <c r="H27" t="n">
-        <v>234549.6</v>
+        <v>235964.25</v>
       </c>
       <c r="I27" t="n">
-        <v>28075.09</v>
+        <v>27881.04</v>
       </c>
       <c r="J27" t="n">
-        <v>56390.23091561231</v>
+        <v>54589.386829303</v>
       </c>
       <c r="K27" t="n">
-        <v>56390.23</v>
+        <v>54589.39</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>85887.13</v>
+        <v>87273.03999999999</v>
       </c>
       <c r="N27" t="n">
-        <v>85887.13</v>
+        <v>87273.03999999999</v>
       </c>
       <c r="O27" t="n">
-        <v>170352.45</v>
+        <v>169743.46</v>
       </c>
       <c r="P27" t="n">
-        <v>64179</v>
+        <v>66190.7</v>
       </c>
       <c r="Q27" t="n">
-        <v>64197.15</v>
+        <v>66220.78</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -2487,13 +2487,13 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>64197.15</v>
+        <v>66220.78</v>
       </c>
       <c r="V27" t="n">
-        <v>64197.15</v>
+        <v>66220.78</v>
       </c>
       <c r="W27" t="n">
-        <v>64197.15</v>
+        <v>66220.78</v>
       </c>
     </row>
     <row r="28">
@@ -2514,61 +2514,61 @@
         <v>0.0433</v>
       </c>
       <c r="E28" t="n">
-        <v>4.000819403307661</v>
+        <v>4.032581255524034</v>
       </c>
       <c r="F28" t="n">
-        <v>-4845299.68</v>
+        <v>-4874350.47</v>
       </c>
       <c r="G28" t="n">
-        <v>6500678.84</v>
+        <v>6505925.18</v>
       </c>
       <c r="H28" t="n">
-        <v>1655379.16</v>
+        <v>1631574.71</v>
       </c>
       <c r="I28" t="n">
-        <v>28619.35</v>
+        <v>28281.71</v>
       </c>
       <c r="J28" t="n">
-        <v>66137.51888691494</v>
+        <v>63839.41162908764</v>
       </c>
       <c r="K28" t="n">
-        <v>66137.52</v>
+        <v>63839.41</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>96914.46000000001</v>
+        <v>98112.60000000001</v>
       </c>
       <c r="N28" t="n">
-        <v>96914.46000000001</v>
+        <v>98112.60000000001</v>
       </c>
       <c r="O28" t="n">
-        <v>191671.33</v>
+        <v>190233.72</v>
       </c>
       <c r="P28" t="n">
-        <v>1463840</v>
+        <v>1441458.67</v>
       </c>
       <c r="Q28" t="n">
-        <v>1463707.83</v>
+        <v>1441340.99</v>
       </c>
       <c r="R28" t="n">
-        <v>95390.55</v>
+        <v>92336.45</v>
       </c>
       <c r="S28" t="n">
-        <v>356073.95</v>
+        <v>347481.32</v>
       </c>
       <c r="T28" t="n">
-        <v>451464.5</v>
+        <v>439817.77</v>
       </c>
       <c r="U28" t="n">
-        <v>1012243.33</v>
+        <v>1001523.22</v>
       </c>
       <c r="V28" t="n">
-        <v>1463707.83</v>
+        <v>1441340.99</v>
       </c>
       <c r="W28" t="n">
-        <v>1012243.33</v>
+        <v>1001523.22</v>
       </c>
     </row>
     <row r="29">
@@ -2589,43 +2589,43 @@
         <v>0.0433</v>
       </c>
       <c r="E29" t="n">
-        <v>4.155237008808432</v>
+        <v>4.18354581497919</v>
       </c>
       <c r="F29" t="n">
-        <v>2894817.5</v>
+        <v>2657842.05</v>
       </c>
       <c r="G29" t="n">
-        <v>-1294862.39</v>
+        <v>-1068753.37</v>
       </c>
       <c r="H29" t="n">
-        <v>1599955.11</v>
+        <v>1589088.68</v>
       </c>
       <c r="I29" t="n">
-        <v>49036.9</v>
+        <v>49725.58</v>
       </c>
       <c r="J29" t="n">
-        <v>81816.61745331844</v>
+        <v>78880.50503346871</v>
       </c>
       <c r="K29" t="n">
-        <v>81816.62</v>
+        <v>78880.50999999999</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>112517.3</v>
+        <v>113615.88</v>
       </c>
       <c r="N29" t="n">
-        <v>112517.3</v>
+        <v>113615.88</v>
       </c>
       <c r="O29" t="n">
-        <v>243370.82</v>
+        <v>242221.96</v>
       </c>
       <c r="P29" t="n">
-        <v>1356077.08</v>
+        <v>1346807.52</v>
       </c>
       <c r="Q29" t="n">
-        <v>1356584.29</v>
+        <v>1346866.71</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -2637,13 +2637,13 @@
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1356584.29</v>
+        <v>1346866.71</v>
       </c>
       <c r="V29" t="n">
-        <v>1356584.29</v>
+        <v>1346866.71</v>
       </c>
       <c r="W29" t="n">
-        <v>1356584.29</v>
+        <v>1346866.71</v>
       </c>
     </row>
     <row r="30">
@@ -2664,43 +2664,43 @@
         <v>0.0433</v>
       </c>
       <c r="E30" t="n">
-        <v>4.292409812557828</v>
+        <v>4.320174560062103</v>
       </c>
       <c r="F30" t="n">
-        <v>10018446.98</v>
+        <v>9987806.83</v>
       </c>
       <c r="G30" t="n">
-        <v>-9764412.52</v>
+        <v>-9724392.119999999</v>
       </c>
       <c r="H30" t="n">
-        <v>254034.47</v>
+        <v>263414.71</v>
       </c>
       <c r="I30" t="n">
-        <v>39825.84</v>
+        <v>39443.06</v>
       </c>
       <c r="J30" t="n">
-        <v>89510.63215673738</v>
+        <v>86292.45377524965</v>
       </c>
       <c r="K30" t="n">
-        <v>89510.63</v>
+        <v>86292.45</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>119166.35</v>
+        <v>120348.28</v>
       </c>
       <c r="N30" t="n">
-        <v>119166.35</v>
+        <v>120348.28</v>
       </c>
       <c r="O30" t="n">
-        <v>248502.82</v>
+        <v>246083.79</v>
       </c>
       <c r="P30" t="n">
-        <v>5642.25</v>
+        <v>17446.2</v>
       </c>
       <c r="Q30" t="n">
-        <v>5531.64</v>
+        <v>17330.92</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -2712,13 +2712,13 @@
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>5531.64</v>
+        <v>17330.92</v>
       </c>
       <c r="V30" t="n">
-        <v>5531.64</v>
+        <v>17330.92</v>
       </c>
       <c r="W30" t="n">
-        <v>5531.64</v>
+        <v>17330.92</v>
       </c>
     </row>
     <row r="31">
@@ -2739,61 +2739,61 @@
         <v>0.0433</v>
       </c>
       <c r="E31" t="n">
-        <v>4.337311205890681</v>
+        <v>4.366989380953362</v>
       </c>
       <c r="F31" t="n">
-        <v>6219009.94</v>
+        <v>6509044.86</v>
       </c>
       <c r="G31" t="n">
-        <v>-5875259.41</v>
+        <v>-6173438.07</v>
       </c>
       <c r="H31" t="n">
-        <v>343750.53</v>
+        <v>335606.79</v>
       </c>
       <c r="I31" t="n">
-        <v>26110.49</v>
+        <v>26437.3</v>
       </c>
       <c r="J31" t="n">
-        <v>87997.70040974021</v>
+        <v>84939.72050010308</v>
       </c>
       <c r="K31" t="n">
-        <v>87997.7</v>
+        <v>84939.72</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>115115.06</v>
+        <v>116420.62</v>
       </c>
       <c r="N31" t="n">
-        <v>115115.06</v>
+        <v>116420.62</v>
       </c>
       <c r="O31" t="n">
-        <v>229223.25</v>
+        <v>227797.64</v>
       </c>
       <c r="P31" t="n">
-        <v>114242.97</v>
+        <v>107519.93</v>
       </c>
       <c r="Q31" t="n">
-        <v>114527.28</v>
+        <v>107809.15</v>
       </c>
       <c r="R31" t="n">
-        <v>106008</v>
+        <v>102687.2</v>
       </c>
       <c r="S31" t="n">
-        <v>205815.18</v>
+        <v>218402.62</v>
       </c>
       <c r="T31" t="n">
-        <v>311823.17</v>
+        <v>321089.82</v>
       </c>
       <c r="U31" t="n">
-        <v>-197295.89</v>
+        <v>-213280.67</v>
       </c>
       <c r="V31" t="n">
-        <v>114527.28</v>
+        <v>107809.15</v>
       </c>
       <c r="W31" t="n">
-        <v>-197295.89</v>
+        <v>-213280.67</v>
       </c>
     </row>
     <row r="32">
@@ -2814,43 +2814,43 @@
         <v>0.0433</v>
       </c>
       <c r="E32" t="n">
-        <v>4.243653152040969</v>
+        <v>4.272485561619262</v>
       </c>
       <c r="F32" t="n">
-        <v>4082108.32</v>
+        <v>4383878.01</v>
       </c>
       <c r="G32" t="n">
-        <v>-3523925.75</v>
+        <v>-3833541.57</v>
       </c>
       <c r="H32" t="n">
-        <v>558182.5699999999</v>
+        <v>550336.4300000001</v>
       </c>
       <c r="I32" t="n">
-        <v>27263.61</v>
+        <v>27021.68</v>
       </c>
       <c r="J32" t="n">
-        <v>107410.6345902989</v>
+        <v>103666.6805898625</v>
       </c>
       <c r="K32" t="n">
-        <v>107410.63</v>
+        <v>103666.68</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>125134.09</v>
+        <v>126425.78</v>
       </c>
       <c r="N32" t="n">
-        <v>125134.09</v>
+        <v>126425.78</v>
       </c>
       <c r="O32" t="n">
-        <v>259808.33</v>
+        <v>257114.14</v>
       </c>
       <c r="P32" t="n">
-        <v>298737.41</v>
+        <v>293571.62</v>
       </c>
       <c r="Q32" t="n">
-        <v>298374.24</v>
+        <v>293222.29</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -2862,13 +2862,13 @@
         <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>298374.24</v>
+        <v>293222.29</v>
       </c>
       <c r="V32" t="n">
-        <v>298374.24</v>
+        <v>293222.29</v>
       </c>
       <c r="W32" t="n">
-        <v>298374.24</v>
+        <v>293222.29</v>
       </c>
     </row>
     <row r="33">
@@ -2889,43 +2889,43 @@
         <v>0.0433</v>
       </c>
       <c r="E33" t="n">
-        <v>4.314163112947152</v>
+        <v>4.333535961437725</v>
       </c>
       <c r="F33" t="n">
-        <v>1308117.89</v>
+        <v>1056342.4</v>
       </c>
       <c r="G33" t="n">
-        <v>-793416.67</v>
+        <v>-523432.75</v>
       </c>
       <c r="H33" t="n">
-        <v>514701.23</v>
+        <v>532909.65</v>
       </c>
       <c r="I33" t="n">
-        <v>41153.21</v>
+        <v>40213.95</v>
       </c>
       <c r="J33" t="n">
-        <v>121680.6973342472</v>
+        <v>117735.0293862985</v>
       </c>
       <c r="K33" t="n">
-        <v>121680.7</v>
+        <v>117735.03</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>120597.51</v>
+        <v>121690.98</v>
       </c>
       <c r="N33" t="n">
-        <v>120597.51</v>
+        <v>121690.98</v>
       </c>
       <c r="O33" t="n">
-        <v>283431.42</v>
+        <v>279639.96</v>
       </c>
       <c r="P33" t="n">
-        <v>229440.52</v>
+        <v>251513.82</v>
       </c>
       <c r="Q33" t="n">
-        <v>231269.81</v>
+        <v>253269.69</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>231269.81</v>
+        <v>253269.69</v>
       </c>
       <c r="V33" t="n">
-        <v>231269.81</v>
+        <v>253269.69</v>
       </c>
       <c r="W33" t="n">
-        <v>231269.81</v>
+        <v>253269.69</v>
       </c>
     </row>
     <row r="34">
@@ -2964,61 +2964,61 @@
         <v>0.0409</v>
       </c>
       <c r="E34" t="n">
-        <v>4.424262340213177</v>
+        <v>4.440402956285593</v>
       </c>
       <c r="F34" t="n">
-        <v>8428167.15</v>
+        <v>7938181.62</v>
       </c>
       <c r="G34" t="n">
-        <v>-8273395.92</v>
+        <v>-7770282.02</v>
       </c>
       <c r="H34" t="n">
-        <v>154771.23</v>
+        <v>167899.6</v>
       </c>
       <c r="I34" t="n">
-        <v>40769.83</v>
+        <v>39739.48</v>
       </c>
       <c r="J34" t="n">
-        <v>139577.0344012068</v>
+        <v>135460.6899180207</v>
       </c>
       <c r="K34" t="n">
-        <v>139577.03</v>
+        <v>135460.69</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>123342.93</v>
+        <v>124402.17</v>
       </c>
       <c r="N34" t="n">
-        <v>123342.93</v>
+        <v>124402.17</v>
       </c>
       <c r="O34" t="n">
-        <v>303689.8</v>
+        <v>299602.34</v>
       </c>
       <c r="P34" t="n">
-        <v>-143145.54</v>
+        <v>-126159.95</v>
       </c>
       <c r="Q34" t="n">
-        <v>-148918.56</v>
+        <v>-131702.74</v>
       </c>
       <c r="R34" t="n">
-        <v>112145.01</v>
+        <v>109192.96</v>
       </c>
       <c r="S34" t="n">
-        <v>38627</v>
+        <v>42835.1</v>
       </c>
       <c r="T34" t="n">
-        <v>150772.01</v>
+        <v>152028.06</v>
       </c>
       <c r="U34" t="n">
-        <v>-299690.57</v>
+        <v>-283730.8</v>
       </c>
       <c r="V34" t="n">
-        <v>-148918.56</v>
+        <v>-131702.74</v>
       </c>
       <c r="W34" t="n">
-        <v>-299690.57</v>
+        <v>-283730.8</v>
       </c>
     </row>
     <row r="35">
@@ -3039,43 +3039,43 @@
         <v>0.0386</v>
       </c>
       <c r="E35" t="n">
-        <v>4.439295723762534</v>
+        <v>4.466021121437486</v>
       </c>
       <c r="F35" t="n">
-        <v>3535848.32</v>
+        <v>4329440.42</v>
       </c>
       <c r="G35" t="n">
-        <v>-2630683.7</v>
+        <v>-3430145.87</v>
       </c>
       <c r="H35" t="n">
-        <v>905164.61</v>
+        <v>899294.55</v>
       </c>
       <c r="I35" t="n">
-        <v>41508.31</v>
+        <v>41909.22</v>
       </c>
       <c r="J35" t="n">
-        <v>158390.7621401346</v>
+        <v>154273.5420871677</v>
       </c>
       <c r="K35" t="n">
-        <v>158390.76</v>
+        <v>154273.54</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>131030.05</v>
+        <v>132625.46</v>
       </c>
       <c r="N35" t="n">
-        <v>131030.05</v>
+        <v>132625.46</v>
       </c>
       <c r="O35" t="n">
-        <v>330929.12</v>
+        <v>328808.23</v>
       </c>
       <c r="P35" t="n">
-        <v>573869.51</v>
+        <v>570108.0699999999</v>
       </c>
       <c r="Q35" t="n">
-        <v>574235.49</v>
+        <v>570486.3199999999</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -3087,13 +3087,13 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>574235.49</v>
+        <v>570486.3199999999</v>
       </c>
       <c r="V35" t="n">
-        <v>574235.49</v>
+        <v>570486.3199999999</v>
       </c>
       <c r="W35" t="n">
-        <v>574235.49</v>
+        <v>570486.3199999999</v>
       </c>
     </row>
     <row r="36">
@@ -3114,43 +3114,43 @@
         <v>0.0388</v>
       </c>
       <c r="E36" t="n">
-        <v>4.375956524981069</v>
+        <v>4.397124345432636</v>
       </c>
       <c r="F36" t="n">
-        <v>-6020348.23</v>
+        <v>-6022867.31</v>
       </c>
       <c r="G36" t="n">
-        <v>6034160.92</v>
+        <v>6038037.69</v>
       </c>
       <c r="H36" t="n">
-        <v>13812.69</v>
+        <v>15170.37</v>
       </c>
       <c r="I36" t="n">
-        <v>57831.1</v>
+        <v>58107.02</v>
       </c>
       <c r="J36" t="n">
-        <v>132244.5458945951</v>
+        <v>129026.7630641025</v>
       </c>
       <c r="K36" t="n">
-        <v>132244.55</v>
+        <v>129026.76</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>102333</v>
+        <v>103465.77</v>
       </c>
       <c r="N36" t="n">
-        <v>102333</v>
+        <v>103465.77</v>
       </c>
       <c r="O36" t="n">
-        <v>292408.65</v>
+        <v>290599.55</v>
       </c>
       <c r="P36" t="n">
-        <v>-277966.74</v>
+        <v>-274826.73</v>
       </c>
       <c r="Q36" t="n">
-        <v>-278595.96</v>
+        <v>-275429.17</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -3162,13 +3162,13 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>-278595.96</v>
+        <v>-275429.17</v>
       </c>
       <c r="V36" t="n">
-        <v>-278595.96</v>
+        <v>-275429.17</v>
       </c>
       <c r="W36" t="n">
-        <v>-278595.96</v>
+        <v>-275429.17</v>
       </c>
     </row>
     <row r="37">
@@ -3189,61 +3189,61 @@
         <v>0.0365</v>
       </c>
       <c r="E37" t="n">
-        <v>4.48874428325304</v>
+        <v>4.499831911575786</v>
       </c>
       <c r="F37" t="n">
-        <v>-1432409.34</v>
+        <v>-1443486.14</v>
       </c>
       <c r="G37" t="n">
-        <v>2565550.75</v>
+        <v>2563871.36</v>
       </c>
       <c r="H37" t="n">
-        <v>1133141.4</v>
+        <v>1120385.22</v>
       </c>
       <c r="I37" t="n">
-        <v>26347.25</v>
+        <v>25621.98</v>
       </c>
       <c r="J37" t="n">
-        <v>159409.3399601358</v>
+        <v>155644.9534730969</v>
       </c>
       <c r="K37" t="n">
-        <v>159409.34</v>
+        <v>155644.95</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>120314.81</v>
+        <v>121189.46</v>
       </c>
       <c r="N37" t="n">
-        <v>120314.81</v>
+        <v>121189.46</v>
       </c>
       <c r="O37" t="n">
-        <v>306071.4</v>
+        <v>302456.4</v>
       </c>
       <c r="P37" t="n">
-        <v>828170.92</v>
+        <v>818984.7</v>
       </c>
       <c r="Q37" t="n">
-        <v>827070</v>
+        <v>817928.83</v>
       </c>
       <c r="R37" t="n">
-        <v>113296.79</v>
+        <v>110468.93</v>
       </c>
       <c r="S37" t="n">
-        <v>146794.28</v>
+        <v>159126.92</v>
       </c>
       <c r="T37" t="n">
-        <v>260091.07</v>
+        <v>269595.85</v>
       </c>
       <c r="U37" t="n">
-        <v>566978.9399999999</v>
+        <v>548332.97</v>
       </c>
       <c r="V37" t="n">
-        <v>827070</v>
+        <v>817928.83</v>
       </c>
       <c r="W37" t="n">
-        <v>566978.9399999999</v>
+        <v>548332.97</v>
       </c>
     </row>
     <row r="38">
@@ -3264,43 +3264,43 @@
         <v>0.0363</v>
       </c>
       <c r="E38" t="n">
-        <v>4.578251486178021</v>
+        <v>4.590864073496129</v>
       </c>
       <c r="F38" t="n">
-        <v>1119726.71</v>
+        <v>1255108.95</v>
       </c>
       <c r="G38" t="n">
-        <v>-274719.49</v>
+        <v>-442245.91</v>
       </c>
       <c r="H38" t="n">
-        <v>845007.22</v>
+        <v>812863.05</v>
       </c>
       <c r="I38" t="n">
-        <v>43970.55</v>
+        <v>44116.36</v>
       </c>
       <c r="J38" t="n">
-        <v>156989.4925524802</v>
+        <v>153030.0146938253</v>
       </c>
       <c r="K38" t="n">
-        <v>156989.49</v>
+        <v>153030.01</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>113032.13</v>
+        <v>113810.01</v>
       </c>
       <c r="N38" t="n">
-        <v>113032.13</v>
+        <v>113810.01</v>
       </c>
       <c r="O38" t="n">
-        <v>313992.18</v>
+        <v>310956.39</v>
       </c>
       <c r="P38" t="n">
-        <v>531603.34</v>
+        <v>502478.25</v>
       </c>
       <c r="Q38" t="n">
-        <v>531015.05</v>
+        <v>501906.66</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -3312,13 +3312,13 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>531015.05</v>
+        <v>501906.66</v>
       </c>
       <c r="V38" t="n">
-        <v>531015.05</v>
+        <v>501906.66</v>
       </c>
       <c r="W38" t="n">
-        <v>531015.05</v>
+        <v>501906.66</v>
       </c>
     </row>
     <row r="39">
@@ -3339,43 +3339,43 @@
         <v>0.0363</v>
       </c>
       <c r="E39" t="n">
-        <v>4.519924205026048</v>
+        <v>4.529627094944181</v>
       </c>
       <c r="F39" t="n">
-        <v>-3907411.25</v>
+        <v>-4224997.63</v>
       </c>
       <c r="G39" t="n">
-        <v>6406182.98</v>
+        <v>6701569.23</v>
       </c>
       <c r="H39" t="n">
-        <v>2498771.72</v>
+        <v>2476571.6</v>
       </c>
       <c r="I39" t="n">
-        <v>46156.18</v>
+        <v>45858.84</v>
       </c>
       <c r="J39" t="n">
-        <v>168931.0708225083</v>
+        <v>164354.7817473046</v>
       </c>
       <c r="K39" t="n">
-        <v>168931.07</v>
+        <v>164354.78</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>111333.83</v>
+        <v>111814.6</v>
       </c>
       <c r="N39" t="n">
-        <v>111333.83</v>
+        <v>111814.6</v>
       </c>
       <c r="O39" t="n">
-        <v>326421.08</v>
+        <v>322028.22</v>
       </c>
       <c r="P39" t="n">
-        <v>2172579.94</v>
+        <v>2155390.79</v>
       </c>
       <c r="Q39" t="n">
-        <v>2172350.65</v>
+        <v>2154543.38</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -3387,13 +3387,13 @@
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>2172350.65</v>
+        <v>2154543.38</v>
       </c>
       <c r="V39" t="n">
-        <v>2172350.65</v>
+        <v>2154543.38</v>
       </c>
       <c r="W39" t="n">
-        <v>2172350.65</v>
+        <v>2154543.38</v>
       </c>
     </row>
     <row r="40">
@@ -3414,136 +3414,61 @@
         <v>0.0364</v>
       </c>
       <c r="E40" t="n">
-        <v>4.601938104014417</v>
+        <v>4.61634757947121</v>
       </c>
       <c r="F40" t="n">
-        <v>-2860017.83</v>
+        <v>-2758792.11</v>
       </c>
       <c r="G40" t="n">
-        <v>4258916.51</v>
+        <v>4145678.15</v>
       </c>
       <c r="H40" t="n">
-        <v>1398898.69</v>
+        <v>1386886.04</v>
       </c>
       <c r="I40" t="n">
-        <v>45125.31</v>
+        <v>44091.62</v>
       </c>
       <c r="J40" t="n">
-        <v>228098.8668659362</v>
+        <v>222446.1334788338</v>
       </c>
       <c r="K40" t="n">
-        <v>228098.87</v>
+        <v>222446.13</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>139646.67</v>
+        <v>140392.45</v>
       </c>
       <c r="N40" t="n">
-        <v>139646.67</v>
+        <v>140392.45</v>
       </c>
       <c r="O40" t="n">
-        <v>412870.85</v>
+        <v>406930.2</v>
       </c>
       <c r="P40" t="n">
-        <v>986010.24</v>
+        <v>979924.5699999999</v>
       </c>
       <c r="Q40" t="n">
-        <v>986027.84</v>
+        <v>979955.84</v>
       </c>
       <c r="R40" t="n">
-        <v>117673.92</v>
+        <v>115209</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>117673.92</v>
+        <v>115209</v>
       </c>
       <c r="U40" t="n">
-        <v>868353.92</v>
+        <v>864746.84</v>
       </c>
       <c r="V40" t="n">
-        <v>986027.84</v>
+        <v>979955.84</v>
       </c>
       <c r="W40" t="n">
-        <v>868353.92</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Diamond Creek Fund</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>0.03633</v>
-      </c>
-      <c r="D41" t="n">
-        <v>0.0363</v>
-      </c>
-      <c r="E41" t="n">
-        <v>4.754286995688718</v>
-      </c>
-      <c r="F41" t="n">
-        <v>11761649.26</v>
-      </c>
-      <c r="G41" t="n">
-        <v>-12072502.01</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-310852.76</v>
-      </c>
-      <c r="I41" t="n">
-        <v>46120.04</v>
-      </c>
-      <c r="J41" t="n">
-        <v>110732.3973792512</v>
-      </c>
-      <c r="K41" t="n">
-        <v>110732.4</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" t="n">
-        <v>69355.5</v>
-      </c>
-      <c r="N41" t="n">
-        <v>69355.5</v>
-      </c>
-      <c r="O41" t="n">
-        <v>226207.93</v>
-      </c>
-      <c r="P41" t="n">
-        <v>-537060.6899999999</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>-537060.6899999999</v>
-      </c>
-      <c r="R41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" t="n">
-        <v>0</v>
-      </c>
-      <c r="U41" t="n">
-        <v>-537060.6899999999</v>
-      </c>
-      <c r="V41" t="n">
-        <v>-537060.6899999999</v>
-      </c>
-      <c r="W41" t="n">
-        <v>-537060.6899999999</v>
+        <v>864746.84</v>
       </c>
     </row>
   </sheetData>
@@ -3629,37 +3554,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25023405.33</v>
+        <v>25408313.16</v>
       </c>
       <c r="C2" t="n">
-        <v>1015531.17</v>
+        <v>954300.48</v>
       </c>
       <c r="D2" t="n">
-        <v>2516092.17</v>
+        <v>2331436.31</v>
       </c>
       <c r="E2" t="n">
-        <v>4114390.54</v>
+        <v>4070722.97</v>
       </c>
       <c r="F2" t="n">
-        <v>7646013.87</v>
+        <v>7356459.77</v>
       </c>
       <c r="G2" t="n">
-        <v>17675141.23</v>
+        <v>18327795.96</v>
       </c>
       <c r="H2" t="n">
-        <v>17377391.46</v>
+        <v>18051853.39</v>
       </c>
       <c r="I2" t="n">
-        <v>1146719.66</v>
+        <v>1126414.88</v>
       </c>
       <c r="J2" t="n">
-        <v>2320918.9</v>
+        <v>2240992.18</v>
       </c>
       <c r="K2" t="n">
-        <v>3467638.56</v>
+        <v>3367407.06</v>
       </c>
       <c r="L2" t="n">
-        <v>13909752.9</v>
+        <v>14684446.33</v>
       </c>
     </row>
   </sheetData>
